--- a/data/out/test2/001317375_Python版_2pt.xlsx
+++ b/data/out/test2/001317375_Python版_2pt.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet'!$A$1:$CB$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet'!$A$1:$CC$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -159,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -172,20 +172,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -193,7 +192,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -206,34 +204,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -241,7 +232,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -251,6 +245,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -627,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:CA45"/>
+  <dimension ref="B2:CB45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.625" defaultRowHeight="18.25" customHeight="1"/>
   <sheetData>
     <row r="2">
@@ -682,9 +679,10 @@
       <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
       <c r="AE3" s="5"/>
+      <c r="AF3" s="6"/>
     </row>
     <row r="4">
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>業務名</t>
         </is>
@@ -694,14 +692,14 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>○○管内交通量検討業務</t>
         </is>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>10,800,000円（消費税込み）</t>
         </is>
@@ -714,7 +712,7 @@
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="5"/>
-      <c r="T4" s="6" t="inlineStr">
+      <c r="T4" s="7" t="inlineStr">
         <is>
           <t>管理技術者</t>
         </is>
@@ -722,7 +720,7 @@
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
       <c r="W4" s="5"/>
-      <c r="X4" s="6" t="inlineStr">
+      <c r="X4" s="7" t="inlineStr">
         <is>
           <t>○○○○</t>
         </is>
@@ -734,31 +732,59 @@
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
       <c r="AE4" s="5"/>
+      <c r="AF4" s="6"/>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>工期（自）</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>H31.1.10</t>
         </is>
       </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="10" t="inlineStr">
         <is>
           <t>担当技術者（副）</t>
         </is>
       </c>
-      <c r="X5" s="8" t="inlineStr">
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="10" t="inlineStr">
         <is>
           <t>□□□□</t>
         </is>
       </c>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="4"/>
+      <c r="AD5" s="4"/>
+      <c r="AE5" s="5"/>
+      <c r="AF5" s="6"/>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>工期（至）</t>
         </is>
@@ -768,13 +794,13 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>R1.12.20</t>
         </is>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>R1.12.20</t>
         </is>
@@ -782,6 +808,25 @@
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="5"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
+      <c r="AA6" s="11"/>
+      <c r="AB6" s="11"/>
+      <c r="AC6" s="11"/>
+      <c r="AD6" s="11"/>
+      <c r="AE6" s="11"/>
+      <c r="AF6" s="6"/>
     </row>
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
@@ -794,13 +839,13 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="9"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
+      <c r="N7" s="9"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
@@ -866,9 +911,10 @@
       <c r="BY7" s="4"/>
       <c r="BZ7" s="4"/>
       <c r="CA7" s="5"/>
+      <c r="CB7" s="12"/>
     </row>
     <row r="8">
-      <c r="B8" s="10"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
@@ -885,28 +931,28 @@
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="10"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="10"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="10"/>
-      <c r="Y8" s="13" t="inlineStr">
+      <c r="S8" s="13"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="14" t="inlineStr">
         <is>
           <t>着手日</t>
         </is>
       </c>
-      <c r="Z8" s="12"/>
-      <c r="AA8" s="14" t="inlineStr">
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="15" t="inlineStr">
         <is>
           <t>完了日</t>
         </is>
       </c>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="10"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="6"/>
       <c r="AD8" s="11"/>
-      <c r="AE8" s="12"/>
-      <c r="AF8" s="15"/>
+      <c r="AE8" s="13"/>
+      <c r="AF8" s="9"/>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
       <c r="AI8" s="4"/>
@@ -929,7 +975,7 @@
       <c r="AZ8" s="4"/>
       <c r="BA8" s="4"/>
       <c r="BB8" s="4"/>
-      <c r="BC8" s="7" t="inlineStr">
+      <c r="BC8" s="8" t="inlineStr">
         <is>
           <t>2019年</t>
         </is>
@@ -958,6 +1004,7 @@
       <c r="BY8" s="4"/>
       <c r="BZ8" s="4"/>
       <c r="CA8" s="5"/>
+      <c r="CB8" s="12"/>
     </row>
     <row r="9">
       <c r="B9" s="16"/>
@@ -1010,105 +1057,106 @@
         </is>
       </c>
       <c r="AE9" s="19"/>
-      <c r="AF9" s="15"/>
+      <c r="AF9" s="9"/>
       <c r="AG9" s="4"/>
-      <c r="AH9" s="7" t="inlineStr">
+      <c r="AH9" s="8" t="inlineStr">
         <is>
           <t>1月</t>
         </is>
       </c>
       <c r="AI9" s="5"/>
-      <c r="AJ9" s="15"/>
+      <c r="AJ9" s="9"/>
       <c r="AK9" s="4"/>
-      <c r="AL9" s="7" t="inlineStr">
+      <c r="AL9" s="8" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
       <c r="AM9" s="5"/>
-      <c r="AN9" s="15"/>
+      <c r="AN9" s="9"/>
       <c r="AO9" s="4"/>
-      <c r="AP9" s="7" t="inlineStr">
+      <c r="AP9" s="8" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
       <c r="AQ9" s="5"/>
-      <c r="AR9" s="15"/>
+      <c r="AR9" s="9"/>
       <c r="AS9" s="4"/>
-      <c r="AT9" s="7" t="inlineStr">
+      <c r="AT9" s="8" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
       <c r="AU9" s="5"/>
-      <c r="AV9" s="15"/>
+      <c r="AV9" s="9"/>
       <c r="AW9" s="4"/>
-      <c r="AX9" s="7" t="inlineStr">
+      <c r="AX9" s="8" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
       <c r="AY9" s="5"/>
-      <c r="AZ9" s="15"/>
+      <c r="AZ9" s="9"/>
       <c r="BA9" s="4"/>
-      <c r="BB9" s="7" t="inlineStr">
+      <c r="BB9" s="8" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
       <c r="BC9" s="5"/>
-      <c r="BD9" s="15"/>
+      <c r="BD9" s="9"/>
       <c r="BE9" s="4"/>
-      <c r="BF9" s="7" t="inlineStr">
+      <c r="BF9" s="8" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
       <c r="BG9" s="5"/>
-      <c r="BH9" s="15"/>
+      <c r="BH9" s="9"/>
       <c r="BI9" s="4"/>
-      <c r="BJ9" s="7" t="inlineStr">
+      <c r="BJ9" s="8" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
       <c r="BK9" s="4"/>
-      <c r="BL9" s="5"/>
-      <c r="BM9" s="15"/>
-      <c r="BN9" s="7" t="inlineStr">
+      <c r="BL9" s="22"/>
+      <c r="BM9" s="9"/>
+      <c r="BN9" s="8" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
       </c>
       <c r="BO9" s="4"/>
       <c r="BP9" s="5"/>
-      <c r="BQ9" s="15"/>
-      <c r="BR9" s="7" t="inlineStr">
+      <c r="BQ9" s="9"/>
+      <c r="BR9" s="8" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
       <c r="BS9" s="4"/>
       <c r="BT9" s="5"/>
-      <c r="BU9" s="15"/>
-      <c r="BV9" s="7" t="inlineStr">
+      <c r="BU9" s="9"/>
+      <c r="BV9" s="8" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
       <c r="BW9" s="5"/>
-      <c r="BX9" s="15"/>
+      <c r="BX9" s="9"/>
       <c r="BY9" s="4"/>
-      <c r="BZ9" s="7" t="inlineStr">
+      <c r="BZ9" s="8" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
       </c>
       <c r="CA9" s="5"/>
+      <c r="CB9" s="12"/>
     </row>
     <row r="10">
-      <c r="B10" s="10"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -1125,60 +1173,68 @@
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="10"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="6"/>
       <c r="Y10" s="11"/>
-      <c r="Z10" s="12"/>
-      <c r="AA10" s="10"/>
-      <c r="AB10" s="12"/>
-      <c r="AC10" s="10"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="13"/>
+      <c r="AC10" s="6"/>
       <c r="AD10" s="11"/>
-      <c r="AE10" s="12"/>
-      <c r="AF10" s="22"/>
-      <c r="AG10" s="10"/>
+      <c r="AE10" s="13"/>
+      <c r="AF10" s="23"/>
+      <c r="AG10" s="6"/>
       <c r="AH10" s="11"/>
       <c r="AI10" s="11"/>
-      <c r="AJ10" s="11"/>
+      <c r="AJ10" s="6"/>
       <c r="AK10" s="11"/>
-      <c r="AL10" s="12"/>
-      <c r="AM10" s="22"/>
-      <c r="AO10" s="10"/>
-      <c r="AP10" s="12"/>
-      <c r="AQ10" s="22"/>
-      <c r="AR10" s="10"/>
-      <c r="AS10" s="12"/>
-      <c r="AT10" s="22"/>
-      <c r="AV10" s="10"/>
-      <c r="AW10" s="12"/>
-      <c r="AX10" s="22"/>
-      <c r="AZ10" s="10"/>
-      <c r="BA10" s="12"/>
-      <c r="BB10" s="22"/>
-      <c r="BD10" s="10"/>
-      <c r="BE10" s="12"/>
-      <c r="BF10" s="22"/>
-      <c r="BH10" s="10"/>
-      <c r="BI10" s="12"/>
-      <c r="BJ10" s="10"/>
+      <c r="AL10" s="13"/>
+      <c r="AM10" s="23"/>
+      <c r="AN10" s="23"/>
+      <c r="AO10" s="6"/>
+      <c r="AP10" s="13"/>
+      <c r="AQ10" s="23"/>
+      <c r="AR10" s="6"/>
+      <c r="AS10" s="23"/>
+      <c r="AT10" s="23"/>
+      <c r="AU10" s="23"/>
+      <c r="AV10" s="6"/>
+      <c r="AW10" s="13"/>
+      <c r="AX10" s="23"/>
+      <c r="AY10" s="23"/>
+      <c r="AZ10" s="6"/>
+      <c r="BA10" s="13"/>
+      <c r="BB10" s="23"/>
+      <c r="BC10" s="23"/>
+      <c r="BD10" s="6"/>
+      <c r="BE10" s="13"/>
+      <c r="BF10" s="23"/>
+      <c r="BG10" s="23"/>
+      <c r="BH10" s="6"/>
+      <c r="BI10" s="13"/>
+      <c r="BJ10" s="6"/>
       <c r="BK10" s="11"/>
-      <c r="BL10" s="11"/>
+      <c r="BL10" s="6"/>
       <c r="BM10" s="11"/>
-      <c r="BN10" s="12"/>
-      <c r="BO10" s="10"/>
-      <c r="BP10" s="12"/>
-      <c r="BQ10" s="10"/>
+      <c r="BN10" s="13"/>
+      <c r="BO10" s="6"/>
+      <c r="BP10" s="13"/>
+      <c r="BQ10" s="6"/>
       <c r="BR10" s="11"/>
       <c r="BS10" s="11"/>
       <c r="BT10" s="11"/>
-      <c r="BU10" s="12"/>
-      <c r="BV10" s="22"/>
-      <c r="BX10" s="10"/>
-      <c r="BY10" s="12"/>
-      <c r="BZ10" s="22"/>
+      <c r="BU10" s="23"/>
+      <c r="BV10" s="23"/>
+      <c r="BW10" s="23"/>
+      <c r="BX10" s="6"/>
+      <c r="BY10" s="13"/>
+      <c r="BZ10" s="23"/>
+      <c r="CA10" s="23"/>
+      <c r="CB10" s="12"/>
     </row>
     <row r="11">
       <c r="B11" s="20" t="inlineStr">
@@ -1215,7 +1271,7 @@
       <c r="AC11" s="16"/>
       <c r="AD11" s="17"/>
       <c r="AE11" s="19"/>
-      <c r="AF11" s="23"/>
+      <c r="AF11" s="24"/>
       <c r="AG11" s="16"/>
       <c r="AH11" s="18" t="inlineStr">
         <is>
@@ -1226,22 +1282,27 @@
       <c r="AJ11" s="17"/>
       <c r="AK11" s="17"/>
       <c r="AL11" s="19"/>
-      <c r="AM11" s="23"/>
+      <c r="AM11" s="24"/>
+      <c r="AN11" s="24"/>
       <c r="AO11" s="16"/>
       <c r="AP11" s="19"/>
-      <c r="AQ11" s="23"/>
+      <c r="AQ11" s="24"/>
       <c r="AR11" s="16"/>
-      <c r="AS11" s="19"/>
-      <c r="AT11" s="23"/>
+      <c r="AS11" s="24"/>
+      <c r="AT11" s="24"/>
+      <c r="AU11" s="24"/>
       <c r="AV11" s="16"/>
       <c r="AW11" s="19"/>
-      <c r="AX11" s="23"/>
+      <c r="AX11" s="24"/>
+      <c r="AY11" s="24"/>
       <c r="AZ11" s="16"/>
       <c r="BA11" s="19"/>
-      <c r="BB11" s="23"/>
+      <c r="BB11" s="24"/>
+      <c r="BC11" s="24"/>
       <c r="BD11" s="16"/>
       <c r="BE11" s="19"/>
-      <c r="BF11" s="23"/>
+      <c r="BF11" s="24"/>
+      <c r="BG11" s="24"/>
       <c r="BH11" s="16"/>
       <c r="BI11" s="19"/>
       <c r="BJ11" s="16"/>
@@ -1264,13 +1325,16 @@
       <c r="BS11" s="17"/>
       <c r="BT11" s="17"/>
       <c r="BU11" s="19"/>
-      <c r="BV11" s="23"/>
+      <c r="BV11" s="24"/>
+      <c r="BW11" s="24"/>
       <c r="BX11" s="16"/>
       <c r="BY11" s="19"/>
-      <c r="BZ11" s="23"/>
+      <c r="BZ11" s="24"/>
+      <c r="CA11" s="24"/>
+      <c r="CB11" s="12"/>
     </row>
     <row r="12">
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>打合せ</t>
         </is>
@@ -1285,10 +1349,10 @@
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="15"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="9"/>
       <c r="O12" s="4"/>
-      <c r="P12" s="7" t="inlineStr">
+      <c r="P12" s="8" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
@@ -1296,85 +1360,91 @@
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="5"/>
-      <c r="T12" s="15"/>
+      <c r="T12" s="9"/>
       <c r="U12" s="5"/>
-      <c r="V12" s="15"/>
+      <c r="V12" s="9"/>
       <c r="W12" s="5"/>
-      <c r="X12" s="15"/>
+      <c r="X12" s="9"/>
       <c r="Y12" s="4"/>
       <c r="Z12" s="5"/>
-      <c r="AA12" s="15"/>
+      <c r="AA12" s="9"/>
       <c r="AB12" s="5"/>
-      <c r="AC12" s="15"/>
+      <c r="AC12" s="9"/>
       <c r="AD12" s="4"/>
       <c r="AE12" s="5"/>
-      <c r="AF12" s="15"/>
+      <c r="AF12" s="9"/>
       <c r="AG12" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
       <c r="AH12" s="5"/>
-      <c r="AI12" s="24"/>
-      <c r="AJ12" s="2" t="inlineStr">
+      <c r="AI12" s="22"/>
+      <c r="AJ12" s="25" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="AK12" s="15"/>
+      <c r="AK12" s="9"/>
       <c r="AL12" s="5"/>
-      <c r="AM12" s="24"/>
-      <c r="AO12" s="15"/>
+      <c r="AM12" s="22"/>
+      <c r="AN12" s="22"/>
+      <c r="AO12" s="9"/>
       <c r="AP12" s="5"/>
-      <c r="AQ12" s="24"/>
-      <c r="AR12" s="15"/>
+      <c r="AQ12" s="22"/>
+      <c r="AR12" s="9"/>
       <c r="AS12" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
       <c r="AT12" s="5"/>
-      <c r="AU12" s="24"/>
-      <c r="AV12" s="15"/>
+      <c r="AU12" s="22"/>
+      <c r="AV12" s="9"/>
       <c r="AW12" s="5"/>
-      <c r="AX12" s="24"/>
-      <c r="AZ12" s="15"/>
+      <c r="AX12" s="22"/>
+      <c r="AY12" s="22"/>
+      <c r="AZ12" s="9"/>
       <c r="BA12" s="5"/>
-      <c r="BB12" s="24"/>
-      <c r="BD12" s="15"/>
+      <c r="BB12" s="22"/>
+      <c r="BC12" s="22"/>
+      <c r="BD12" s="9"/>
       <c r="BE12" s="5"/>
-      <c r="BF12" s="15"/>
+      <c r="BF12" s="9"/>
       <c r="BG12" s="25" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BH12" s="15"/>
+      <c r="BH12" s="9"/>
       <c r="BI12" s="5"/>
-      <c r="BJ12" s="24"/>
-      <c r="BK12" s="15"/>
-      <c r="BL12" s="5"/>
-      <c r="BM12" s="24"/>
-      <c r="BN12" s="15"/>
+      <c r="BJ12" s="22"/>
+      <c r="BK12" s="9"/>
+      <c r="BL12" s="22"/>
+      <c r="BM12" s="22"/>
+      <c r="BN12" s="9"/>
       <c r="BO12" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
       <c r="BP12" s="5"/>
-      <c r="BQ12" s="15"/>
-      <c r="BR12" s="25" t="inlineStr">
+      <c r="BQ12" s="9"/>
+      <c r="BR12" s="26" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="BS12" s="15"/>
+      <c r="BS12" s="9"/>
       <c r="BT12" s="5"/>
-      <c r="BU12" s="24"/>
-      <c r="BW12" s="24"/>
-      <c r="BX12" s="15"/>
+      <c r="BU12" s="22"/>
+      <c r="BV12" s="22"/>
+      <c r="BW12" s="22"/>
+      <c r="BX12" s="9"/>
       <c r="BY12" s="5"/>
-      <c r="BZ12" s="24"/>
+      <c r="BZ12" s="22"/>
+      <c r="CA12" s="22"/>
+      <c r="CB12" s="12"/>
     </row>
     <row r="13">
       <c r="B13" s="20" t="inlineStr">
@@ -1393,34 +1463,96 @@
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
       <c r="M13" s="19"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="N13" s="9"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="8" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="AG13" s="2" t="inlineStr">
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="5"/>
+      <c r="AA13" s="9"/>
+      <c r="AB13" s="5"/>
+      <c r="AC13" s="9"/>
+      <c r="AD13" s="4"/>
+      <c r="AE13" s="5"/>
+      <c r="AF13" s="9"/>
+      <c r="AG13" s="8" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="AJ13" s="2" t="inlineStr">
+      <c r="AH13" s="5"/>
+      <c r="AI13" s="22"/>
+      <c r="AJ13" s="25" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="AM13" s="2" t="inlineStr">
+      <c r="AK13" s="9"/>
+      <c r="AL13" s="4"/>
+      <c r="AM13" s="25" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="AT13" s="2" t="inlineStr">
+      <c r="AN13" s="22"/>
+      <c r="AO13" s="9"/>
+      <c r="AP13" s="5"/>
+      <c r="AQ13" s="22"/>
+      <c r="AR13" s="9"/>
+      <c r="AS13" s="22"/>
+      <c r="AT13" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
+      <c r="AU13" s="22"/>
+      <c r="AV13" s="9"/>
+      <c r="AW13" s="5"/>
+      <c r="AX13" s="22"/>
+      <c r="AY13" s="22"/>
+      <c r="AZ13" s="9"/>
+      <c r="BA13" s="5"/>
+      <c r="BB13" s="22"/>
+      <c r="BC13" s="22"/>
+      <c r="BD13" s="9"/>
+      <c r="BE13" s="5"/>
+      <c r="BF13" s="22"/>
+      <c r="BG13" s="22"/>
+      <c r="BH13" s="9"/>
+      <c r="BI13" s="5"/>
+      <c r="BJ13" s="22"/>
+      <c r="BK13" s="9"/>
+      <c r="BL13" s="22"/>
+      <c r="BM13" s="22"/>
+      <c r="BN13" s="22"/>
+      <c r="BO13" s="9"/>
+      <c r="BP13" s="5"/>
+      <c r="BQ13" s="22"/>
+      <c r="BR13" s="22"/>
+      <c r="BS13" s="9"/>
+      <c r="BT13" s="5"/>
+      <c r="BU13" s="22"/>
+      <c r="BV13" s="22"/>
+      <c r="BW13" s="22"/>
+      <c r="BX13" s="9"/>
+      <c r="BY13" s="5"/>
+      <c r="BZ13" s="22"/>
+      <c r="CA13" s="22"/>
+      <c r="CB13" s="12"/>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>準備計画</t>
         </is>
@@ -1429,202 +1561,224 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="10"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="6"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="10"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="6"/>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
       <c r="R14" s="11"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="14" t="inlineStr">
+      <c r="S14" s="13"/>
+      <c r="T14" s="15" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="U14" s="12"/>
-      <c r="V14" s="10"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="10"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="6"/>
       <c r="Y14" s="11"/>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="10"/>
-      <c r="AB14" s="12"/>
-      <c r="AC14" s="10"/>
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="13"/>
+      <c r="AC14" s="6"/>
       <c r="AD14" s="11"/>
-      <c r="AE14" s="12"/>
-      <c r="AF14" s="22"/>
-      <c r="AG14" s="10"/>
-      <c r="AH14" s="12"/>
-      <c r="AI14" s="22"/>
-      <c r="AK14" s="10"/>
-      <c r="AL14" s="12"/>
-      <c r="AM14" s="22"/>
-      <c r="AO14" s="10"/>
-      <c r="AP14" s="12"/>
-      <c r="AQ14" s="22"/>
-      <c r="AR14" s="10"/>
-      <c r="AS14" s="12"/>
-      <c r="AT14" s="22"/>
-      <c r="AV14" s="10"/>
-      <c r="AW14" s="12"/>
-      <c r="AX14" s="22"/>
-      <c r="AZ14" s="10"/>
-      <c r="BA14" s="12"/>
-      <c r="BB14" s="22"/>
-      <c r="BD14" s="22"/>
-      <c r="BF14" s="26" t="inlineStr">
+      <c r="AE14" s="13"/>
+      <c r="AF14" s="23"/>
+      <c r="AG14" s="6"/>
+      <c r="AH14" s="13"/>
+      <c r="AI14" s="23"/>
+      <c r="AJ14" s="23"/>
+      <c r="AK14" s="6"/>
+      <c r="AL14" s="13"/>
+      <c r="AM14" s="23"/>
+      <c r="AN14" s="23"/>
+      <c r="AO14" s="6"/>
+      <c r="AP14" s="13"/>
+      <c r="AQ14" s="23"/>
+      <c r="AR14" s="6"/>
+      <c r="AS14" s="23"/>
+      <c r="AT14" s="23"/>
+      <c r="AU14" s="23"/>
+      <c r="AV14" s="6"/>
+      <c r="AW14" s="13"/>
+      <c r="AX14" s="23"/>
+      <c r="AY14" s="23"/>
+      <c r="AZ14" s="6"/>
+      <c r="BA14" s="13"/>
+      <c r="BB14" s="23"/>
+      <c r="BC14" s="23"/>
+      <c r="BD14" s="23"/>
+      <c r="BE14" s="23"/>
+      <c r="BF14" s="27" t="inlineStr">
         <is>
           <t>期間が複数になる場合は「セルの</t>
         </is>
       </c>
-      <c r="BG14" s="8" t="inlineStr">
+      <c r="BG14" s="28" t="inlineStr">
         <is>
           <t>複数に</t>
         </is>
       </c>
-      <c r="BH14" s="27" t="inlineStr">
+      <c r="BH14" s="29" t="inlineStr">
         <is>
           <t>なる場</t>
         </is>
       </c>
-      <c r="BI14" s="12"/>
+      <c r="BI14" s="13"/>
       <c r="BJ14" s="28" t="inlineStr">
         <is>
           <t>合は「</t>
         </is>
       </c>
-      <c r="BK14" s="27" t="inlineStr">
+      <c r="BK14" s="29" t="inlineStr">
         <is>
           <t>セルの</t>
         </is>
       </c>
-      <c r="BL14" s="12"/>
-      <c r="BM14" s="22"/>
-      <c r="BO14" s="10"/>
-      <c r="BP14" s="12"/>
-      <c r="BQ14" s="22"/>
-      <c r="BS14" s="10"/>
-      <c r="BT14" s="12"/>
-      <c r="BU14" s="22"/>
-      <c r="BW14" s="22"/>
-      <c r="BX14" s="10"/>
-      <c r="BY14" s="12"/>
-      <c r="BZ14" s="22"/>
+      <c r="BL14" s="23"/>
+      <c r="BM14" s="23"/>
+      <c r="BN14" s="23"/>
+      <c r="BO14" s="6"/>
+      <c r="BP14" s="13"/>
+      <c r="BQ14" s="23"/>
+      <c r="BR14" s="23"/>
+      <c r="BS14" s="6"/>
+      <c r="BT14" s="13"/>
+      <c r="BU14" s="23"/>
+      <c r="BV14" s="23"/>
+      <c r="BW14" s="23"/>
+      <c r="BX14" s="6"/>
+      <c r="BY14" s="13"/>
+      <c r="BZ14" s="23"/>
+      <c r="CA14" s="23"/>
+      <c r="CB14" s="12"/>
     </row>
     <row r="15">
-      <c r="B15" s="16"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="19"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="21" t="inlineStr">
+      <c r="B15" s="9"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="26" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="18" t="inlineStr">
+      <c r="X15" s="9"/>
+      <c r="Y15" s="8" t="inlineStr">
         <is>
           <t>1月11日</t>
         </is>
       </c>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="20" t="inlineStr">
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="7" t="inlineStr">
         <is>
           <t>1月28日</t>
         </is>
       </c>
-      <c r="AB15" s="19"/>
-      <c r="AC15" s="16"/>
-      <c r="AD15" s="17"/>
-      <c r="AE15" s="21" t="inlineStr">
+      <c r="AB15" s="5"/>
+      <c r="AC15" s="9"/>
+      <c r="AD15" s="4"/>
+      <c r="AE15" s="26" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="AF15" s="23"/>
-      <c r="AG15" s="16"/>
-      <c r="AH15" s="19"/>
-      <c r="AI15" s="23"/>
-      <c r="AK15" s="16"/>
-      <c r="AL15" s="19"/>
-      <c r="AM15" s="23"/>
-      <c r="AO15" s="16"/>
-      <c r="AP15" s="19"/>
-      <c r="AQ15" s="23"/>
-      <c r="AR15" s="16"/>
-      <c r="AS15" s="19"/>
-      <c r="AT15" s="23"/>
-      <c r="AV15" s="16"/>
-      <c r="AW15" s="19"/>
-      <c r="AX15" s="23"/>
-      <c r="AZ15" s="16"/>
-      <c r="BA15" s="19"/>
-      <c r="BB15" s="23"/>
-      <c r="BD15" s="23"/>
-      <c r="BF15" s="29" t="inlineStr">
+      <c r="AF15" s="22"/>
+      <c r="AG15" s="9"/>
+      <c r="AH15" s="5"/>
+      <c r="AI15" s="22"/>
+      <c r="AJ15" s="22"/>
+      <c r="AK15" s="9"/>
+      <c r="AL15" s="5"/>
+      <c r="AM15" s="22"/>
+      <c r="AN15" s="22"/>
+      <c r="AO15" s="9"/>
+      <c r="AP15" s="5"/>
+      <c r="AQ15" s="22"/>
+      <c r="AR15" s="9"/>
+      <c r="AS15" s="22"/>
+      <c r="AT15" s="22"/>
+      <c r="AU15" s="22"/>
+      <c r="AV15" s="9"/>
+      <c r="AW15" s="5"/>
+      <c r="AX15" s="22"/>
+      <c r="AY15" s="22"/>
+      <c r="AZ15" s="9"/>
+      <c r="BA15" s="5"/>
+      <c r="BB15" s="22"/>
+      <c r="BC15" s="22"/>
+      <c r="BD15" s="22"/>
+      <c r="BE15" s="22"/>
+      <c r="BF15" s="25" t="inlineStr">
         <is>
           <t>書式設定」から色を設定することが</t>
         </is>
       </c>
-      <c r="BG15" s="8" t="inlineStr">
+      <c r="BG15" s="30" t="inlineStr">
         <is>
           <t>定」か</t>
         </is>
       </c>
-      <c r="BH15" s="30" t="inlineStr">
+      <c r="BH15" s="10" t="inlineStr">
         <is>
           <t>ら色を</t>
         </is>
       </c>
-      <c r="BI15" s="19"/>
-      <c r="BJ15" s="31" t="inlineStr">
+      <c r="BI15" s="5"/>
+      <c r="BJ15" s="30" t="inlineStr">
         <is>
           <t>設定す</t>
         </is>
       </c>
-      <c r="BK15" s="30" t="inlineStr">
+      <c r="BK15" s="10" t="inlineStr">
         <is>
           <t>ることが</t>
         </is>
       </c>
-      <c r="BL15" s="19"/>
-      <c r="BM15" s="23"/>
-      <c r="BO15" s="16"/>
-      <c r="BP15" s="19"/>
-      <c r="BQ15" s="23"/>
-      <c r="BS15" s="16"/>
-      <c r="BT15" s="19"/>
-      <c r="BU15" s="23"/>
-      <c r="BW15" s="23"/>
-      <c r="BX15" s="16"/>
-      <c r="BY15" s="19"/>
-      <c r="BZ15" s="23"/>
+      <c r="BL15" s="22"/>
+      <c r="BM15" s="22"/>
+      <c r="BN15" s="22"/>
+      <c r="BO15" s="9"/>
+      <c r="BP15" s="5"/>
+      <c r="BQ15" s="22"/>
+      <c r="BR15" s="22"/>
+      <c r="BS15" s="9"/>
+      <c r="BT15" s="5"/>
+      <c r="BU15" s="22"/>
+      <c r="BV15" s="22"/>
+      <c r="BW15" s="22"/>
+      <c r="BX15" s="9"/>
+      <c r="BY15" s="5"/>
+      <c r="BZ15" s="22"/>
+      <c r="CA15" s="22"/>
+      <c r="CB15" s="12"/>
     </row>
     <row r="16">
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>基礎資料収集・整理</t>
         </is>
@@ -1633,8 +1787,8 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="G16" s="13"/>
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>資料収集</t>
         </is>
@@ -1644,7 +1798,7 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="5"/>
-      <c r="N16" s="6" t="inlineStr">
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>作業項目の欄は、柔軟に対応できるようテキスト、罫線完了</t>
         </is>
@@ -1654,73 +1808,84 @@
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
       <c r="S16" s="5"/>
-      <c r="T16" s="9" t="inlineStr">
+      <c r="T16" s="10" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
       <c r="U16" s="5"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="25" t="inlineStr">
+      <c r="V16" s="9"/>
+      <c r="W16" s="26" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="X16" s="15"/>
+      <c r="X16" s="9"/>
       <c r="Y16" s="4"/>
       <c r="Z16" s="5"/>
-      <c r="AA16" s="15"/>
+      <c r="AA16" s="9"/>
       <c r="AB16" s="5"/>
-      <c r="AC16" s="15"/>
+      <c r="AC16" s="9"/>
       <c r="AD16" s="4"/>
       <c r="AE16" s="5"/>
-      <c r="AF16" s="32" t="inlineStr">
+      <c r="AF16" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG16" s="15"/>
+      <c r="AG16" s="9"/>
       <c r="AH16" s="5"/>
-      <c r="AI16" s="24"/>
-      <c r="AK16" s="15"/>
-      <c r="AL16" s="5"/>
-      <c r="AM16" s="24"/>
-      <c r="AO16" s="15"/>
+      <c r="AI16" s="22"/>
+      <c r="AJ16" s="22"/>
+      <c r="AK16" s="9"/>
+      <c r="AL16" s="22"/>
+      <c r="AM16" s="22"/>
+      <c r="AN16" s="22"/>
+      <c r="AO16" s="9"/>
       <c r="AP16" s="5"/>
-      <c r="AQ16" s="24"/>
-      <c r="AR16" s="15"/>
-      <c r="AS16" s="5"/>
-      <c r="AT16" s="24"/>
-      <c r="AV16" s="15"/>
-      <c r="AW16" s="5"/>
-      <c r="AX16" s="24"/>
-      <c r="AZ16" s="15"/>
+      <c r="AQ16" s="22"/>
+      <c r="AR16" s="9"/>
+      <c r="AS16" s="22"/>
+      <c r="AT16" s="22"/>
+      <c r="AU16" s="22"/>
+      <c r="AV16" s="9"/>
+      <c r="AW16" s="22"/>
+      <c r="AX16" s="22"/>
+      <c r="AY16" s="22"/>
+      <c r="AZ16" s="9"/>
       <c r="BA16" s="5"/>
-      <c r="BB16" s="24"/>
-      <c r="BD16" s="15"/>
-      <c r="BE16" s="5"/>
-      <c r="BF16" s="24"/>
-      <c r="BH16" s="15"/>
+      <c r="BB16" s="22"/>
+      <c r="BC16" s="22"/>
+      <c r="BD16" s="9"/>
+      <c r="BE16" s="22"/>
+      <c r="BF16" s="22"/>
+      <c r="BG16" s="22"/>
+      <c r="BH16" s="9"/>
       <c r="BI16" s="5"/>
-      <c r="BJ16" s="24"/>
-      <c r="BK16" s="15"/>
-      <c r="BL16" s="5"/>
-      <c r="BM16" s="24"/>
-      <c r="BO16" s="15"/>
+      <c r="BJ16" s="22"/>
+      <c r="BK16" s="9"/>
+      <c r="BL16" s="22"/>
+      <c r="BM16" s="22"/>
+      <c r="BN16" s="22"/>
+      <c r="BO16" s="9"/>
       <c r="BP16" s="5"/>
-      <c r="BQ16" s="24"/>
-      <c r="BS16" s="15"/>
+      <c r="BQ16" s="22"/>
+      <c r="BR16" s="22"/>
+      <c r="BS16" s="9"/>
       <c r="BT16" s="5"/>
-      <c r="BU16" s="24"/>
-      <c r="BW16" s="24"/>
-      <c r="BX16" s="15"/>
+      <c r="BU16" s="22"/>
+      <c r="BV16" s="22"/>
+      <c r="BW16" s="22"/>
+      <c r="BX16" s="9"/>
       <c r="BY16" s="5"/>
-      <c r="BZ16" s="24"/>
+      <c r="BZ16" s="22"/>
+      <c r="CA16" s="22"/>
+      <c r="CB16" s="12"/>
     </row>
     <row r="17">
-      <c r="B17" s="33"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="27" t="inlineStr">
+      <c r="B17" s="12"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="29" t="inlineStr">
         <is>
           <t>資料整理</t>
         </is>
@@ -1729,66 +1894,98 @@
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="M17" s="13"/>
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>等の編集が可能</t>
         </is>
       </c>
-      <c r="T17" s="35" t="inlineStr">
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="32" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="U17" s="12"/>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="U17" s="13"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="26" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="X17" s="9"/>
+      <c r="Y17" s="8" t="inlineStr">
         <is>
           <t>2月20日</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="Z17" s="5"/>
+      <c r="AA17" s="7" t="inlineStr">
         <is>
           <t>6月10日</t>
         </is>
       </c>
-      <c r="AC17" s="10"/>
+      <c r="AB17" s="5"/>
+      <c r="AC17" s="6"/>
       <c r="AD17" s="11"/>
-      <c r="AE17" s="36" t="inlineStr">
+      <c r="AE17" s="33" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="AF17" s="22"/>
-      <c r="AG17" s="10"/>
-      <c r="AH17" s="12"/>
-      <c r="AI17" s="22"/>
-      <c r="AK17" s="10"/>
-      <c r="AL17" s="12"/>
-      <c r="BB17" s="22"/>
-      <c r="BD17" s="10"/>
-      <c r="BE17" s="12"/>
-      <c r="BF17" s="22"/>
-      <c r="BH17" s="10"/>
-      <c r="BI17" s="12"/>
-      <c r="BJ17" s="22"/>
-      <c r="BK17" s="10"/>
-      <c r="BL17" s="12"/>
-      <c r="BM17" s="22"/>
-      <c r="BO17" s="10"/>
-      <c r="BP17" s="12"/>
-      <c r="BQ17" s="22"/>
-      <c r="BS17" s="10"/>
-      <c r="BT17" s="12"/>
-      <c r="BU17" s="22"/>
-      <c r="BW17" s="22"/>
-      <c r="BX17" s="10"/>
-      <c r="BY17" s="12"/>
-      <c r="BZ17" s="22"/>
+      <c r="AF17" s="23"/>
+      <c r="AG17" s="6"/>
+      <c r="AH17" s="13"/>
+      <c r="AI17" s="23"/>
+      <c r="AJ17" s="23"/>
+      <c r="AK17" s="6"/>
+      <c r="AL17" s="23"/>
+      <c r="AM17" s="22"/>
+      <c r="AN17" s="22"/>
+      <c r="AO17" s="9"/>
+      <c r="AP17" s="5"/>
+      <c r="AQ17" s="22"/>
+      <c r="AR17" s="9"/>
+      <c r="AS17" s="22"/>
+      <c r="AT17" s="22"/>
+      <c r="AU17" s="22"/>
+      <c r="AV17" s="9"/>
+      <c r="AW17" s="5"/>
+      <c r="AX17" s="22"/>
+      <c r="AY17" s="22"/>
+      <c r="AZ17" s="9"/>
+      <c r="BA17" s="5"/>
+      <c r="BB17" s="23"/>
+      <c r="BC17" s="23"/>
+      <c r="BD17" s="6"/>
+      <c r="BE17" s="13"/>
+      <c r="BF17" s="23"/>
+      <c r="BG17" s="23"/>
+      <c r="BH17" s="6"/>
+      <c r="BI17" s="13"/>
+      <c r="BJ17" s="23"/>
+      <c r="BK17" s="6"/>
+      <c r="BL17" s="23"/>
+      <c r="BM17" s="23"/>
+      <c r="BN17" s="23"/>
+      <c r="BO17" s="6"/>
+      <c r="BP17" s="13"/>
+      <c r="BQ17" s="23"/>
+      <c r="BR17" s="23"/>
+      <c r="BS17" s="6"/>
+      <c r="BT17" s="13"/>
+      <c r="BU17" s="23"/>
+      <c r="BV17" s="23"/>
+      <c r="BW17" s="23"/>
+      <c r="BX17" s="6"/>
+      <c r="BY17" s="13"/>
+      <c r="BZ17" s="23"/>
+      <c r="CA17" s="23"/>
+      <c r="CB17" s="12"/>
     </row>
     <row r="18">
       <c r="B18" s="16"/>
@@ -1807,81 +2004,92 @@
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
       <c r="M18" s="19"/>
-      <c r="N18" s="15"/>
+      <c r="N18" s="9"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="5"/>
-      <c r="T18" s="16"/>
+      <c r="T18" s="9"/>
       <c r="U18" s="19"/>
-      <c r="V18" s="15"/>
-      <c r="W18" s="25" t="inlineStr">
+      <c r="V18" s="9"/>
+      <c r="W18" s="26" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="7" t="inlineStr">
+      <c r="X18" s="9"/>
+      <c r="Y18" s="8" t="inlineStr">
         <is>
           <t>2月22日</t>
         </is>
       </c>
       <c r="Z18" s="5"/>
-      <c r="AA18" s="6" t="inlineStr">
+      <c r="AA18" s="7" t="inlineStr">
         <is>
           <t>3月10日</t>
         </is>
       </c>
       <c r="AB18" s="5"/>
-      <c r="AC18" s="16"/>
+      <c r="AC18" s="9"/>
       <c r="AD18" s="17"/>
       <c r="AE18" s="21" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="AF18" s="23"/>
+      <c r="AF18" s="24"/>
       <c r="AG18" s="16"/>
       <c r="AH18" s="19"/>
-      <c r="AI18" s="23"/>
+      <c r="AI18" s="24"/>
+      <c r="AJ18" s="24"/>
       <c r="AK18" s="16"/>
       <c r="AL18" s="19"/>
-      <c r="AM18" s="24"/>
-      <c r="AO18" s="15"/>
+      <c r="AM18" s="22"/>
+      <c r="AN18" s="22"/>
+      <c r="AO18" s="9"/>
       <c r="AP18" s="5"/>
-      <c r="AQ18" s="24"/>
-      <c r="AR18" s="15"/>
-      <c r="AS18" s="5"/>
-      <c r="AT18" s="24"/>
-      <c r="AV18" s="15"/>
+      <c r="AQ18" s="22"/>
+      <c r="AR18" s="9"/>
+      <c r="AS18" s="22"/>
+      <c r="AT18" s="22"/>
+      <c r="AU18" s="22"/>
+      <c r="AV18" s="9"/>
       <c r="AW18" s="5"/>
-      <c r="AX18" s="24"/>
-      <c r="AZ18" s="15"/>
+      <c r="AX18" s="22"/>
+      <c r="AY18" s="22"/>
+      <c r="AZ18" s="9"/>
       <c r="BA18" s="5"/>
-      <c r="BB18" s="23"/>
+      <c r="BB18" s="22"/>
+      <c r="BC18" s="24"/>
       <c r="BD18" s="16"/>
       <c r="BE18" s="19"/>
-      <c r="BF18" s="23"/>
+      <c r="BF18" s="24"/>
+      <c r="BG18" s="24"/>
       <c r="BH18" s="16"/>
       <c r="BI18" s="19"/>
-      <c r="BJ18" s="23"/>
+      <c r="BJ18" s="24"/>
       <c r="BK18" s="16"/>
-      <c r="BL18" s="19"/>
-      <c r="BM18" s="23"/>
+      <c r="BL18" s="24"/>
+      <c r="BM18" s="24"/>
+      <c r="BN18" s="24"/>
       <c r="BO18" s="16"/>
       <c r="BP18" s="19"/>
-      <c r="BQ18" s="23"/>
+      <c r="BQ18" s="24"/>
+      <c r="BR18" s="24"/>
       <c r="BS18" s="16"/>
       <c r="BT18" s="19"/>
-      <c r="BU18" s="23"/>
-      <c r="BW18" s="23"/>
+      <c r="BU18" s="24"/>
+      <c r="BV18" s="24"/>
+      <c r="BW18" s="24"/>
       <c r="BX18" s="16"/>
       <c r="BY18" s="19"/>
-      <c r="BZ18" s="23"/>
+      <c r="BZ18" s="24"/>
+      <c r="CA18" s="24"/>
+      <c r="CB18" s="12"/>
     </row>
     <row r="19">
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>交通量配分用データの作成OD表</t>
         </is>
@@ -1890,8 +2098,8 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="27" t="inlineStr">
+      <c r="G19" s="13"/>
+      <c r="H19" s="29" t="inlineStr">
         <is>
           <t>OD表</t>
         </is>
@@ -1900,93 +2108,102 @@
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="10"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="6"/>
       <c r="O19" s="11"/>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
       <c r="R19" s="11"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="14" t="inlineStr">
+      <c r="S19" s="13"/>
+      <c r="T19" s="15" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="U19" s="12"/>
-      <c r="V19" s="10"/>
-      <c r="W19" s="12"/>
-      <c r="X19" s="10"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="6"/>
       <c r="Y19" s="11"/>
-      <c r="Z19" s="12"/>
-      <c r="AA19" s="10"/>
-      <c r="AB19" s="12"/>
-      <c r="AC19" s="10"/>
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="6"/>
+      <c r="AB19" s="13"/>
+      <c r="AC19" s="6"/>
       <c r="AD19" s="11"/>
-      <c r="AE19" s="12"/>
-      <c r="AF19" s="22"/>
-      <c r="AG19" s="10"/>
-      <c r="AH19" s="12"/>
-      <c r="AI19" s="22"/>
-      <c r="AK19" s="10"/>
-      <c r="AL19" s="12"/>
-      <c r="AM19" s="22"/>
-      <c r="AO19" s="10"/>
-      <c r="AP19" s="12"/>
-      <c r="AQ19" s="22"/>
-      <c r="AR19" s="10"/>
-      <c r="AS19" s="12"/>
+      <c r="AE19" s="13"/>
+      <c r="AF19" s="23"/>
+      <c r="AG19" s="6"/>
+      <c r="AH19" s="13"/>
+      <c r="AI19" s="23"/>
+      <c r="AJ19" s="23"/>
+      <c r="AK19" s="6"/>
+      <c r="AL19" s="13"/>
+      <c r="AM19" s="23"/>
+      <c r="AN19" s="23"/>
+      <c r="AO19" s="6"/>
+      <c r="AP19" s="13"/>
+      <c r="AQ19" s="23"/>
+      <c r="AR19" s="6"/>
+      <c r="AS19" s="23"/>
       <c r="AT19" s="28" t="inlineStr">
         <is>
           <t>ャート</t>
         </is>
       </c>
-      <c r="AU19" s="8" t="inlineStr">
+      <c r="AU19" s="28" t="inlineStr">
         <is>
           <t>は入力</t>
         </is>
       </c>
-      <c r="AV19" s="27" t="inlineStr">
+      <c r="AV19" s="29" t="inlineStr">
         <is>
           <t>した着</t>
         </is>
       </c>
-      <c r="AW19" s="12"/>
+      <c r="AW19" s="13"/>
       <c r="AX19" s="28" t="inlineStr">
         <is>
           <t>手日、</t>
         </is>
       </c>
-      <c r="AY19" s="8" t="inlineStr">
+      <c r="AY19" s="28" t="inlineStr">
         <is>
           <t>完</t>
         </is>
       </c>
-      <c r="AZ19" s="10"/>
-      <c r="BA19" s="12"/>
-      <c r="BB19" s="22"/>
-      <c r="BD19" s="10"/>
-      <c r="BE19" s="12"/>
-      <c r="BF19" s="22"/>
-      <c r="BH19" s="10"/>
-      <c r="BI19" s="12"/>
-      <c r="BJ19" s="22"/>
-      <c r="BK19" s="10"/>
-      <c r="BL19" s="12"/>
-      <c r="BM19" s="22"/>
-      <c r="BO19" s="10"/>
-      <c r="BP19" s="12"/>
-      <c r="BQ19" s="22"/>
-      <c r="BS19" s="10"/>
-      <c r="BT19" s="12"/>
-      <c r="BU19" s="22"/>
-      <c r="BW19" s="22"/>
-      <c r="BX19" s="10"/>
-      <c r="BY19" s="12"/>
-      <c r="BZ19" s="22"/>
+      <c r="AZ19" s="6"/>
+      <c r="BA19" s="13"/>
+      <c r="BB19" s="23"/>
+      <c r="BC19" s="23"/>
+      <c r="BD19" s="6"/>
+      <c r="BE19" s="13"/>
+      <c r="BF19" s="23"/>
+      <c r="BG19" s="23"/>
+      <c r="BH19" s="6"/>
+      <c r="BI19" s="13"/>
+      <c r="BJ19" s="23"/>
+      <c r="BK19" s="6"/>
+      <c r="BL19" s="23"/>
+      <c r="BM19" s="23"/>
+      <c r="BN19" s="23"/>
+      <c r="BO19" s="6"/>
+      <c r="BP19" s="13"/>
+      <c r="BQ19" s="23"/>
+      <c r="BR19" s="23"/>
+      <c r="BS19" s="6"/>
+      <c r="BT19" s="13"/>
+      <c r="BU19" s="23"/>
+      <c r="BV19" s="23"/>
+      <c r="BW19" s="23"/>
+      <c r="BX19" s="6"/>
+      <c r="BY19" s="13"/>
+      <c r="BZ19" s="23"/>
+      <c r="CA19" s="23"/>
+      <c r="CB19" s="12"/>
     </row>
     <row r="20">
-      <c r="B20" s="33"/>
-      <c r="G20" s="34"/>
+      <c r="B20" s="12"/>
+      <c r="G20" s="31"/>
       <c r="H20" s="16"/>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
@@ -2001,101 +2218,110 @@
       <c r="S20" s="19"/>
       <c r="T20" s="16"/>
       <c r="U20" s="19"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="21" t="inlineStr">
+      <c r="V20" s="9"/>
+      <c r="W20" s="26" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="X20" s="16"/>
-      <c r="Y20" s="18" t="inlineStr">
+      <c r="X20" s="9"/>
+      <c r="Y20" s="8" t="inlineStr">
         <is>
           <t>2月5日</t>
         </is>
       </c>
-      <c r="Z20" s="19"/>
-      <c r="AA20" s="20" t="inlineStr">
+      <c r="Z20" s="5"/>
+      <c r="AA20" s="7" t="inlineStr">
         <is>
           <t>3月5日</t>
         </is>
       </c>
-      <c r="AB20" s="19"/>
-      <c r="AC20" s="16"/>
+      <c r="AB20" s="5"/>
+      <c r="AC20" s="9"/>
       <c r="AD20" s="17"/>
       <c r="AE20" s="21" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="AF20" s="23"/>
+      <c r="AF20" s="24"/>
       <c r="AG20" s="16"/>
       <c r="AH20" s="19"/>
-      <c r="AI20" s="23"/>
-      <c r="AK20" s="16"/>
-      <c r="AL20" s="19"/>
-      <c r="AM20" s="23"/>
-      <c r="AO20" s="16"/>
+      <c r="AI20" s="24"/>
+      <c r="AJ20" s="22"/>
+      <c r="AK20" s="9"/>
+      <c r="AL20" s="5"/>
+      <c r="AM20" s="22"/>
+      <c r="AN20" s="22"/>
+      <c r="AO20" s="9"/>
       <c r="AP20" s="19"/>
-      <c r="AQ20" s="23"/>
+      <c r="AQ20" s="24"/>
       <c r="AR20" s="20" t="inlineStr">
         <is>
           <t>バーチャートは入力した着手日、完了日をもとにマクロを使用して表示</t>
         </is>
       </c>
-      <c r="AS20" s="19"/>
-      <c r="AT20" s="31" t="inlineStr">
+      <c r="AS20" s="24"/>
+      <c r="AT20" s="34" t="inlineStr">
         <is>
           <t>もとに</t>
         </is>
       </c>
-      <c r="AU20" s="8" t="inlineStr">
+      <c r="AU20" s="34" t="inlineStr">
         <is>
           <t>マクロ</t>
         </is>
       </c>
-      <c r="AV20" s="30" t="inlineStr">
+      <c r="AV20" s="35" t="inlineStr">
         <is>
           <t>を使用</t>
         </is>
       </c>
       <c r="AW20" s="19"/>
-      <c r="AX20" s="31" t="inlineStr">
+      <c r="AX20" s="34" t="inlineStr">
         <is>
           <t>して表</t>
         </is>
       </c>
-      <c r="AY20" s="8" t="inlineStr">
+      <c r="AY20" s="34" t="inlineStr">
         <is>
           <t>示</t>
         </is>
       </c>
       <c r="AZ20" s="16"/>
       <c r="BA20" s="19"/>
-      <c r="BB20" s="23"/>
+      <c r="BB20" s="24"/>
+      <c r="BC20" s="24"/>
       <c r="BD20" s="16"/>
       <c r="BE20" s="19"/>
-      <c r="BF20" s="23"/>
+      <c r="BF20" s="24"/>
+      <c r="BG20" s="24"/>
       <c r="BH20" s="16"/>
       <c r="BI20" s="19"/>
-      <c r="BJ20" s="23"/>
+      <c r="BJ20" s="24"/>
       <c r="BK20" s="16"/>
-      <c r="BL20" s="19"/>
-      <c r="BM20" s="23"/>
+      <c r="BL20" s="24"/>
+      <c r="BM20" s="24"/>
+      <c r="BN20" s="24"/>
       <c r="BO20" s="16"/>
       <c r="BP20" s="19"/>
-      <c r="BQ20" s="23"/>
+      <c r="BQ20" s="24"/>
+      <c r="BR20" s="24"/>
       <c r="BS20" s="16"/>
       <c r="BT20" s="19"/>
-      <c r="BU20" s="23"/>
-      <c r="BW20" s="23"/>
+      <c r="BU20" s="24"/>
+      <c r="BV20" s="24"/>
+      <c r="BW20" s="24"/>
       <c r="BX20" s="16"/>
       <c r="BY20" s="19"/>
-      <c r="BZ20" s="23"/>
+      <c r="BZ20" s="24"/>
+      <c r="CA20" s="24"/>
+      <c r="CB20" s="12"/>
     </row>
     <row r="21">
-      <c r="B21" s="33"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="B21" s="12"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>ゾーニング</t>
         </is>
@@ -2105,108 +2331,118 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="5"/>
-      <c r="N21" s="15"/>
+      <c r="N21" s="9"/>
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
       <c r="S21" s="5"/>
-      <c r="T21" s="6" t="inlineStr">
+      <c r="T21" s="7" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
       <c r="U21" s="5"/>
-      <c r="V21" s="15"/>
-      <c r="W21" s="25" t="inlineStr">
+      <c r="V21" s="9"/>
+      <c r="W21" s="26" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="X21" s="15"/>
-      <c r="Y21" s="7" t="inlineStr">
+      <c r="X21" s="9"/>
+      <c r="Y21" s="8" t="inlineStr">
         <is>
           <t>2月10日</t>
         </is>
       </c>
       <c r="Z21" s="5"/>
-      <c r="AA21" s="6" t="inlineStr">
+      <c r="AA21" s="7" t="inlineStr">
         <is>
           <t>3月10日</t>
         </is>
       </c>
       <c r="AB21" s="5"/>
-      <c r="AC21" s="15"/>
+      <c r="AC21" s="9"/>
       <c r="AD21" s="4"/>
-      <c r="AE21" s="25" t="inlineStr">
+      <c r="AE21" s="26" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="AF21" s="24"/>
-      <c r="AG21" s="15"/>
+      <c r="AF21" s="22"/>
+      <c r="AG21" s="9"/>
       <c r="AH21" s="5"/>
-      <c r="AI21" s="24"/>
-      <c r="AK21" s="15"/>
+      <c r="AI21" s="22"/>
+      <c r="AJ21" s="22"/>
+      <c r="AK21" s="9"/>
       <c r="AL21" s="5"/>
-      <c r="AM21" s="24"/>
-      <c r="AO21" s="15"/>
+      <c r="AM21" s="22"/>
+      <c r="AN21" s="22"/>
+      <c r="AO21" s="9"/>
       <c r="AP21" s="5"/>
-      <c r="AQ21" s="24"/>
-      <c r="AR21" s="15"/>
-      <c r="AS21" s="5"/>
-      <c r="AT21" s="24"/>
-      <c r="AV21" s="15"/>
+      <c r="AQ21" s="22"/>
+      <c r="AR21" s="9"/>
+      <c r="AS21" s="22"/>
+      <c r="AT21" s="22"/>
+      <c r="AU21" s="22"/>
+      <c r="AV21" s="9"/>
       <c r="AW21" s="5"/>
-      <c r="AX21" s="24"/>
-      <c r="AZ21" s="15"/>
+      <c r="AX21" s="22"/>
+      <c r="AY21" s="22"/>
+      <c r="AZ21" s="9"/>
       <c r="BA21" s="5"/>
-      <c r="BB21" s="24"/>
-      <c r="BD21" s="15"/>
+      <c r="BB21" s="22"/>
+      <c r="BC21" s="22"/>
+      <c r="BD21" s="9"/>
       <c r="BE21" s="25" t="inlineStr">
         <is>
           <t>更新日を赤線で自動表示</t>
         </is>
       </c>
-      <c r="BF21" s="37" t="inlineStr">
+      <c r="BF21" s="30" t="inlineStr">
         <is>
           <t>新日を</t>
         </is>
       </c>
-      <c r="BG21" s="8" t="inlineStr">
+      <c r="BG21" s="30" t="inlineStr">
         <is>
           <t>赤線で</t>
         </is>
       </c>
-      <c r="BH21" s="9" t="inlineStr">
+      <c r="BH21" s="10" t="inlineStr">
         <is>
           <t>自動表</t>
         </is>
       </c>
       <c r="BI21" s="5"/>
-      <c r="BJ21" s="37" t="inlineStr">
+      <c r="BJ21" s="30" t="inlineStr">
         <is>
           <t>示</t>
         </is>
       </c>
-      <c r="BK21" s="15"/>
-      <c r="BL21" s="5"/>
-      <c r="BM21" s="24"/>
-      <c r="BO21" s="15"/>
+      <c r="BK21" s="9"/>
+      <c r="BL21" s="22"/>
+      <c r="BM21" s="22"/>
+      <c r="BN21" s="22"/>
+      <c r="BO21" s="9"/>
       <c r="BP21" s="5"/>
-      <c r="BQ21" s="24"/>
-      <c r="BS21" s="15"/>
+      <c r="BQ21" s="22"/>
+      <c r="BR21" s="22"/>
+      <c r="BS21" s="9"/>
       <c r="BT21" s="5"/>
-      <c r="BU21" s="24"/>
-      <c r="BW21" s="24"/>
-      <c r="BX21" s="15"/>
+      <c r="BU21" s="22"/>
+      <c r="BV21" s="22"/>
+      <c r="BW21" s="22"/>
+      <c r="BX21" s="9"/>
       <c r="BY21" s="5"/>
-      <c r="BZ21" s="24"/>
+      <c r="BZ21" s="22"/>
+      <c r="CA21" s="22"/>
+      <c r="CB21" s="12"/>
     </row>
     <row r="22">
-      <c r="B22" s="33"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="27" t="inlineStr">
+      <c r="B22" s="12"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="29" t="inlineStr">
         <is>
           <t>交通量配分道路網の作成</t>
         </is>
@@ -2215,59 +2451,90 @@
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="10"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="6"/>
       <c r="O22" s="11"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="11"/>
       <c r="R22" s="11"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="10"/>
-      <c r="U22" s="12"/>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="S22" s="13"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="13"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="26" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="X22" s="9"/>
+      <c r="Y22" s="8" t="inlineStr">
         <is>
           <t>2月10日</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
+      <c r="Z22" s="5"/>
+      <c r="AA22" s="7" t="inlineStr">
         <is>
           <t>4月10日</t>
         </is>
       </c>
-      <c r="AC22" s="10"/>
+      <c r="AB22" s="5"/>
+      <c r="AC22" s="6"/>
       <c r="AD22" s="11"/>
-      <c r="AE22" s="36" t="inlineStr">
+      <c r="AE22" s="33" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="AF22" s="22"/>
-      <c r="AG22" s="10"/>
-      <c r="AH22" s="12"/>
-      <c r="AI22" s="22"/>
-      <c r="AU22" s="22"/>
-      <c r="AV22" s="10"/>
-      <c r="AW22" s="12"/>
-      <c r="AX22" s="22"/>
-      <c r="AZ22" s="10"/>
-      <c r="BA22" s="12"/>
-      <c r="BB22" s="22"/>
-      <c r="BM22" s="22"/>
-      <c r="BO22" s="10"/>
-      <c r="BP22" s="12"/>
-      <c r="BQ22" s="22"/>
-      <c r="BS22" s="10"/>
-      <c r="BT22" s="12"/>
-      <c r="BU22" s="22"/>
-      <c r="BW22" s="22"/>
-      <c r="BX22" s="10"/>
-      <c r="BY22" s="12"/>
-      <c r="BZ22" s="22"/>
+      <c r="AF22" s="23"/>
+      <c r="AG22" s="6"/>
+      <c r="AH22" s="13"/>
+      <c r="AI22" s="23"/>
+      <c r="AJ22" s="23"/>
+      <c r="AK22" s="9"/>
+      <c r="AL22" s="5"/>
+      <c r="AM22" s="22"/>
+      <c r="AN22" s="22"/>
+      <c r="AO22" s="9"/>
+      <c r="AP22" s="22"/>
+      <c r="AQ22" s="22"/>
+      <c r="AR22" s="9"/>
+      <c r="AS22" s="22"/>
+      <c r="AT22" s="22"/>
+      <c r="AU22" s="23"/>
+      <c r="AV22" s="6"/>
+      <c r="AW22" s="13"/>
+      <c r="AX22" s="23"/>
+      <c r="AY22" s="23"/>
+      <c r="AZ22" s="6"/>
+      <c r="BA22" s="13"/>
+      <c r="BB22" s="23"/>
+      <c r="BC22" s="23"/>
+      <c r="BD22" s="9"/>
+      <c r="BE22" s="22"/>
+      <c r="BF22" s="22"/>
+      <c r="BG22" s="22"/>
+      <c r="BH22" s="9"/>
+      <c r="BI22" s="5"/>
+      <c r="BJ22" s="22"/>
+      <c r="BK22" s="9"/>
+      <c r="BL22" s="22"/>
+      <c r="BM22" s="23"/>
+      <c r="BN22" s="23"/>
+      <c r="BO22" s="6"/>
+      <c r="BP22" s="13"/>
+      <c r="BQ22" s="23"/>
+      <c r="BR22" s="23"/>
+      <c r="BS22" s="6"/>
+      <c r="BT22" s="13"/>
+      <c r="BU22" s="23"/>
+      <c r="BV22" s="23"/>
+      <c r="BW22" s="23"/>
+      <c r="BX22" s="6"/>
+      <c r="BY22" s="13"/>
+      <c r="BZ22" s="23"/>
+      <c r="CA22" s="23"/>
+      <c r="CB22" s="12"/>
     </row>
     <row r="23">
       <c r="B23" s="16"/>
@@ -2298,79 +2565,90 @@
         </is>
       </c>
       <c r="U23" s="19"/>
-      <c r="V23" s="15"/>
-      <c r="W23" s="25" t="inlineStr">
+      <c r="V23" s="9"/>
+      <c r="W23" s="26" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="7" t="inlineStr">
+      <c r="X23" s="9"/>
+      <c r="Y23" s="8" t="inlineStr">
         <is>
           <t>2月10日</t>
         </is>
       </c>
       <c r="Z23" s="5"/>
-      <c r="AA23" s="6" t="inlineStr">
+      <c r="AA23" s="7" t="inlineStr">
         <is>
           <t>4月20日</t>
         </is>
       </c>
       <c r="AB23" s="5"/>
-      <c r="AC23" s="16"/>
+      <c r="AC23" s="9"/>
       <c r="AD23" s="17"/>
       <c r="AE23" s="21" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="AF23" s="23"/>
+      <c r="AF23" s="24"/>
       <c r="AG23" s="16"/>
       <c r="AH23" s="19"/>
-      <c r="AI23" s="23"/>
-      <c r="AK23" s="15"/>
+      <c r="AI23" s="24"/>
+      <c r="AJ23" s="24"/>
+      <c r="AK23" s="9"/>
       <c r="AL23" s="5"/>
-      <c r="AM23" s="24"/>
-      <c r="AO23" s="15"/>
+      <c r="AM23" s="22"/>
+      <c r="AN23" s="22"/>
+      <c r="AO23" s="9"/>
       <c r="AP23" s="5"/>
-      <c r="AQ23" s="24"/>
-      <c r="AR23" s="15"/>
-      <c r="AS23" s="5"/>
-      <c r="AU23" s="23"/>
+      <c r="AQ23" s="22"/>
+      <c r="AR23" s="9"/>
+      <c r="AS23" s="22"/>
+      <c r="AT23" s="22"/>
+      <c r="AU23" s="22"/>
       <c r="AV23" s="16"/>
       <c r="AW23" s="19"/>
-      <c r="AX23" s="23"/>
+      <c r="AX23" s="24"/>
+      <c r="AY23" s="24"/>
       <c r="AZ23" s="16"/>
       <c r="BA23" s="19"/>
-      <c r="BB23" s="23"/>
-      <c r="BD23" s="15"/>
-      <c r="BE23" s="5"/>
-      <c r="BF23" s="24"/>
-      <c r="BH23" s="15"/>
+      <c r="BB23" s="24"/>
+      <c r="BC23" s="24"/>
+      <c r="BD23" s="9"/>
+      <c r="BE23" s="22"/>
+      <c r="BF23" s="22"/>
+      <c r="BG23" s="22"/>
+      <c r="BH23" s="9"/>
       <c r="BI23" s="5"/>
-      <c r="BJ23" s="24"/>
-      <c r="BK23" s="15"/>
-      <c r="BL23" s="5"/>
-      <c r="BM23" s="23"/>
+      <c r="BJ23" s="22"/>
+      <c r="BK23" s="9"/>
+      <c r="BL23" s="22"/>
+      <c r="BM23" s="22"/>
+      <c r="BN23" s="24"/>
       <c r="BO23" s="16"/>
       <c r="BP23" s="19"/>
-      <c r="BQ23" s="23"/>
+      <c r="BQ23" s="24"/>
+      <c r="BR23" s="24"/>
       <c r="BS23" s="16"/>
       <c r="BT23" s="19"/>
-      <c r="BU23" s="23"/>
-      <c r="BW23" s="23"/>
+      <c r="BU23" s="24"/>
+      <c r="BV23" s="24"/>
+      <c r="BW23" s="24"/>
       <c r="BX23" s="16"/>
       <c r="BY23" s="19"/>
-      <c r="BZ23" s="23"/>
+      <c r="BZ23" s="24"/>
+      <c r="CA23" s="24"/>
+      <c r="CB23" s="12"/>
     </row>
     <row r="24">
-      <c r="B24" s="10"/>
+      <c r="B24" s="6"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="27" t="inlineStr">
+      <c r="G24" s="13"/>
+      <c r="H24" s="29" t="inlineStr">
         <is>
           <t>現況配分計算</t>
         </is>
@@ -2379,81 +2657,98 @@
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="10"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="6"/>
       <c r="O24" s="11"/>
       <c r="P24" s="11"/>
       <c r="Q24" s="11"/>
       <c r="R24" s="11"/>
-      <c r="S24" s="12"/>
-      <c r="T24" s="10"/>
-      <c r="U24" s="12"/>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="S24" s="13"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="13"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="26" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="X24" s="9"/>
+      <c r="Y24" s="8" t="inlineStr">
         <is>
           <t>4月1日</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
+      <c r="Z24" s="5"/>
+      <c r="AA24" s="7" t="inlineStr">
         <is>
           <t>4月15日</t>
         </is>
       </c>
-      <c r="AC24" s="10"/>
+      <c r="AB24" s="5"/>
+      <c r="AC24" s="6"/>
       <c r="AD24" s="11"/>
-      <c r="AE24" s="36" t="inlineStr">
+      <c r="AE24" s="33" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AF24" s="22"/>
-      <c r="AG24" s="10"/>
-      <c r="AH24" s="12"/>
-      <c r="AI24" s="22"/>
-      <c r="AK24" s="10"/>
-      <c r="AL24" s="12"/>
-      <c r="AM24" s="22"/>
-      <c r="AO24" s="10"/>
-      <c r="AP24" s="12"/>
-      <c r="AQ24" s="22"/>
-      <c r="AT24" s="24"/>
-      <c r="AV24" s="10"/>
-      <c r="AW24" s="12"/>
-      <c r="AX24" s="22"/>
-      <c r="AZ24" s="10"/>
-      <c r="BA24" s="12"/>
-      <c r="BB24" s="22"/>
-      <c r="BD24" s="10"/>
-      <c r="BE24" s="12"/>
-      <c r="BF24" s="22"/>
-      <c r="BH24" s="10"/>
-      <c r="BI24" s="12"/>
-      <c r="BJ24" s="22"/>
-      <c r="BK24" s="10"/>
-      <c r="BL24" s="12"/>
-      <c r="BM24" s="22"/>
-      <c r="BO24" s="10"/>
-      <c r="BP24" s="12"/>
-      <c r="BQ24" s="22"/>
-      <c r="BS24" s="10"/>
-      <c r="BT24" s="12"/>
-      <c r="BU24" s="22"/>
-      <c r="BW24" s="22"/>
-      <c r="BX24" s="10"/>
-      <c r="BY24" s="12"/>
-      <c r="BZ24" s="22"/>
+      <c r="AF24" s="23"/>
+      <c r="AG24" s="6"/>
+      <c r="AH24" s="13"/>
+      <c r="AI24" s="23"/>
+      <c r="AJ24" s="23"/>
+      <c r="AK24" s="6"/>
+      <c r="AL24" s="13"/>
+      <c r="AM24" s="23"/>
+      <c r="AN24" s="23"/>
+      <c r="AO24" s="6"/>
+      <c r="AP24" s="13"/>
+      <c r="AQ24" s="23"/>
+      <c r="AR24" s="9"/>
+      <c r="AS24" s="22"/>
+      <c r="AT24" s="22"/>
+      <c r="AU24" s="23"/>
+      <c r="AV24" s="6"/>
+      <c r="AW24" s="13"/>
+      <c r="AX24" s="23"/>
+      <c r="AY24" s="23"/>
+      <c r="AZ24" s="6"/>
+      <c r="BA24" s="13"/>
+      <c r="BB24" s="23"/>
+      <c r="BC24" s="23"/>
+      <c r="BD24" s="6"/>
+      <c r="BE24" s="13"/>
+      <c r="BF24" s="23"/>
+      <c r="BG24" s="23"/>
+      <c r="BH24" s="6"/>
+      <c r="BI24" s="13"/>
+      <c r="BJ24" s="23"/>
+      <c r="BK24" s="6"/>
+      <c r="BL24" s="23"/>
+      <c r="BM24" s="23"/>
+      <c r="BN24" s="23"/>
+      <c r="BO24" s="6"/>
+      <c r="BP24" s="13"/>
+      <c r="BQ24" s="23"/>
+      <c r="BR24" s="23"/>
+      <c r="BS24" s="6"/>
+      <c r="BT24" s="13"/>
+      <c r="BU24" s="23"/>
+      <c r="BV24" s="23"/>
+      <c r="BW24" s="23"/>
+      <c r="BX24" s="6"/>
+      <c r="BY24" s="13"/>
+      <c r="BZ24" s="23"/>
+      <c r="CA24" s="23"/>
+      <c r="CB24" s="12"/>
     </row>
     <row r="25">
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>交通量配分用データの作成現況配分計算</t>
         </is>
       </c>
-      <c r="G25" s="34"/>
+      <c r="G25" s="31"/>
       <c r="H25" s="16"/>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
@@ -2472,74 +2767,86 @@
         </is>
       </c>
       <c r="U25" s="19"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="25" t="inlineStr">
+      <c r="V25" s="9"/>
+      <c r="W25" s="26" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="7" t="inlineStr">
+      <c r="X25" s="9"/>
+      <c r="Y25" s="8" t="inlineStr">
         <is>
           <t>4月1日</t>
         </is>
       </c>
       <c r="Z25" s="5"/>
-      <c r="AA25" s="6" t="inlineStr">
+      <c r="AA25" s="7" t="inlineStr">
         <is>
           <t>4月18日</t>
         </is>
       </c>
       <c r="AB25" s="5"/>
-      <c r="AC25" s="16"/>
+      <c r="AC25" s="9"/>
       <c r="AD25" s="17"/>
       <c r="AE25" s="21" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="AF25" s="23"/>
+      <c r="AF25" s="24"/>
       <c r="AG25" s="16"/>
       <c r="AH25" s="19"/>
-      <c r="AI25" s="23"/>
+      <c r="AI25" s="24"/>
+      <c r="AJ25" s="24"/>
       <c r="AK25" s="16"/>
       <c r="AL25" s="19"/>
-      <c r="AM25" s="23"/>
+      <c r="AM25" s="24"/>
+      <c r="AN25" s="24"/>
       <c r="AO25" s="16"/>
       <c r="AP25" s="19"/>
-      <c r="AQ25" s="23"/>
-      <c r="AR25" s="15"/>
-      <c r="AS25" s="5"/>
+      <c r="AQ25" s="24"/>
+      <c r="AR25" s="9"/>
+      <c r="AS25" s="22"/>
+      <c r="AT25" s="22"/>
+      <c r="AU25" s="22"/>
       <c r="AV25" s="16"/>
       <c r="AW25" s="19"/>
-      <c r="AX25" s="23"/>
+      <c r="AX25" s="24"/>
+      <c r="AY25" s="24"/>
       <c r="AZ25" s="16"/>
       <c r="BA25" s="19"/>
-      <c r="BB25" s="23"/>
+      <c r="BB25" s="24"/>
+      <c r="BC25" s="24"/>
       <c r="BD25" s="16"/>
       <c r="BE25" s="19"/>
-      <c r="BF25" s="23"/>
+      <c r="BF25" s="24"/>
+      <c r="BG25" s="24"/>
       <c r="BH25" s="16"/>
       <c r="BI25" s="19"/>
-      <c r="BJ25" s="23"/>
+      <c r="BJ25" s="24"/>
       <c r="BK25" s="16"/>
-      <c r="BL25" s="19"/>
-      <c r="BM25" s="23"/>
+      <c r="BL25" s="24"/>
+      <c r="BM25" s="24"/>
+      <c r="BN25" s="24"/>
       <c r="BO25" s="16"/>
       <c r="BP25" s="19"/>
-      <c r="BQ25" s="23"/>
+      <c r="BQ25" s="24"/>
+      <c r="BR25" s="24"/>
       <c r="BS25" s="16"/>
       <c r="BT25" s="19"/>
-      <c r="BU25" s="23"/>
-      <c r="BW25" s="23"/>
+      <c r="BU25" s="24"/>
+      <c r="BV25" s="24"/>
+      <c r="BW25" s="24"/>
       <c r="BX25" s="16"/>
       <c r="BY25" s="19"/>
-      <c r="BZ25" s="23"/>
+      <c r="BZ25" s="24"/>
+      <c r="CA25" s="24"/>
+      <c r="CB25" s="12"/>
     </row>
     <row r="26">
-      <c r="B26" s="33"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="B26" s="12"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>将来配分計算</t>
         </is>
@@ -2549,81 +2856,98 @@
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="5"/>
-      <c r="N26" s="15"/>
+      <c r="N26" s="9"/>
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
       <c r="S26" s="5"/>
-      <c r="T26" s="39" t="inlineStr">
+      <c r="T26" s="37" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
       <c r="U26" s="5"/>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="V26" s="9"/>
+      <c r="W26" s="26" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="X26" s="9"/>
+      <c r="Y26" s="8" t="inlineStr">
         <is>
           <t>4月15日</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
+      <c r="Z26" s="5"/>
+      <c r="AA26" s="7" t="inlineStr">
         <is>
           <t>8月10日</t>
         </is>
       </c>
-      <c r="AC26" s="15"/>
+      <c r="AB26" s="5"/>
+      <c r="AC26" s="9"/>
       <c r="AD26" s="4"/>
-      <c r="AE26" s="25" t="inlineStr">
+      <c r="AE26" s="26" t="inlineStr">
         <is>
           <t>117</t>
         </is>
       </c>
-      <c r="AF26" s="24"/>
-      <c r="AG26" s="15"/>
+      <c r="AF26" s="22"/>
+      <c r="AG26" s="9"/>
       <c r="AH26" s="5"/>
-      <c r="AI26" s="24"/>
-      <c r="AK26" s="15"/>
+      <c r="AI26" s="22"/>
+      <c r="AJ26" s="22"/>
+      <c r="AK26" s="9"/>
       <c r="AL26" s="5"/>
-      <c r="AM26" s="24"/>
-      <c r="AO26" s="15"/>
+      <c r="AM26" s="22"/>
+      <c r="AN26" s="22"/>
+      <c r="AO26" s="9"/>
       <c r="AP26" s="5"/>
-      <c r="AQ26" s="24"/>
-      <c r="AT26" s="24"/>
-      <c r="AV26" s="15"/>
+      <c r="AQ26" s="22"/>
+      <c r="AR26" s="9"/>
+      <c r="AS26" s="22"/>
+      <c r="AT26" s="22"/>
+      <c r="AU26" s="22"/>
+      <c r="AV26" s="9"/>
       <c r="AW26" s="5"/>
-      <c r="AX26" s="24"/>
-      <c r="AZ26" s="15"/>
+      <c r="AX26" s="22"/>
+      <c r="AY26" s="22"/>
+      <c r="AZ26" s="9"/>
       <c r="BA26" s="5"/>
-      <c r="BB26" s="24"/>
-      <c r="BD26" s="15"/>
+      <c r="BB26" s="22"/>
+      <c r="BC26" s="22"/>
+      <c r="BD26" s="9"/>
       <c r="BE26" s="5"/>
-      <c r="BF26" s="24"/>
-      <c r="BH26" s="15"/>
+      <c r="BF26" s="22"/>
+      <c r="BG26" s="22"/>
+      <c r="BH26" s="9"/>
       <c r="BI26" s="5"/>
-      <c r="BJ26" s="24"/>
-      <c r="BK26" s="15"/>
-      <c r="BL26" s="5"/>
-      <c r="BM26" s="24"/>
-      <c r="BO26" s="15"/>
+      <c r="BJ26" s="22"/>
+      <c r="BK26" s="9"/>
+      <c r="BL26" s="22"/>
+      <c r="BM26" s="22"/>
+      <c r="BN26" s="22"/>
+      <c r="BO26" s="9"/>
       <c r="BP26" s="5"/>
-      <c r="BQ26" s="24"/>
-      <c r="BS26" s="15"/>
+      <c r="BQ26" s="22"/>
+      <c r="BR26" s="22"/>
+      <c r="BS26" s="9"/>
       <c r="BT26" s="5"/>
-      <c r="BU26" s="24"/>
-      <c r="BW26" s="24"/>
-      <c r="BX26" s="15"/>
+      <c r="BU26" s="22"/>
+      <c r="BV26" s="22"/>
+      <c r="BW26" s="22"/>
+      <c r="BX26" s="9"/>
       <c r="BY26" s="5"/>
-      <c r="BZ26" s="24"/>
+      <c r="BZ26" s="22"/>
+      <c r="CA26" s="22"/>
+      <c r="CB26" s="12"/>
     </row>
     <row r="27">
-      <c r="B27" s="33"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="27" t="inlineStr">
+      <c r="B27" s="12"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="29" t="inlineStr">
         <is>
           <t>集計整理</t>
         </is>
@@ -2632,75 +2956,90 @@
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="10"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="6"/>
       <c r="O27" s="11"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="11"/>
       <c r="R27" s="11"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="10"/>
-      <c r="U27" s="12"/>
-      <c r="V27" s="15"/>
-      <c r="W27" s="25" t="inlineStr">
+      <c r="S27" s="13"/>
+      <c r="T27" s="6"/>
+      <c r="U27" s="13"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="26" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="X27" s="15"/>
-      <c r="Y27" s="7" t="inlineStr">
+      <c r="X27" s="9"/>
+      <c r="Y27" s="8" t="inlineStr">
         <is>
           <t>4月15日</t>
         </is>
       </c>
       <c r="Z27" s="5"/>
-      <c r="AA27" s="6" t="inlineStr">
+      <c r="AA27" s="7" t="inlineStr">
         <is>
           <t>9月20日</t>
         </is>
       </c>
       <c r="AB27" s="5"/>
-      <c r="AC27" s="10"/>
+      <c r="AC27" s="6"/>
       <c r="AD27" s="11"/>
-      <c r="AE27" s="12"/>
-      <c r="AF27" s="22"/>
-      <c r="AG27" s="10"/>
-      <c r="AH27" s="12"/>
-      <c r="AI27" s="22"/>
-      <c r="AK27" s="10"/>
-      <c r="AL27" s="12"/>
-      <c r="AM27" s="22"/>
-      <c r="AO27" s="10"/>
-      <c r="AP27" s="12"/>
-      <c r="AQ27" s="22"/>
-      <c r="AR27" s="10"/>
-      <c r="AS27" s="12"/>
-      <c r="AT27" s="22"/>
-      <c r="AV27" s="10"/>
-      <c r="AW27" s="12"/>
+      <c r="AE27" s="13"/>
+      <c r="AF27" s="23"/>
+      <c r="AG27" s="6"/>
+      <c r="AH27" s="13"/>
+      <c r="AI27" s="23"/>
+      <c r="AJ27" s="23"/>
+      <c r="AK27" s="6"/>
+      <c r="AL27" s="13"/>
+      <c r="AM27" s="23"/>
+      <c r="AN27" s="23"/>
+      <c r="AO27" s="6"/>
+      <c r="AP27" s="13"/>
+      <c r="AQ27" s="23"/>
+      <c r="AR27" s="6"/>
+      <c r="AS27" s="23"/>
+      <c r="AT27" s="23"/>
+      <c r="AU27" s="22"/>
+      <c r="AV27" s="9"/>
+      <c r="AW27" s="5"/>
       <c r="AX27" s="22"/>
-      <c r="AZ27" s="10"/>
-      <c r="BA27" s="12"/>
+      <c r="AY27" s="22"/>
+      <c r="AZ27" s="9"/>
+      <c r="BA27" s="5"/>
       <c r="BB27" s="22"/>
-      <c r="BD27" s="10"/>
-      <c r="BE27" s="12"/>
+      <c r="BC27" s="22"/>
+      <c r="BD27" s="9"/>
+      <c r="BE27" s="5"/>
       <c r="BF27" s="22"/>
-      <c r="BH27" s="10"/>
-      <c r="BI27" s="12"/>
-      <c r="BO27" s="10"/>
-      <c r="BP27" s="12"/>
-      <c r="BQ27" s="22"/>
-      <c r="BS27" s="10"/>
-      <c r="BT27" s="12"/>
-      <c r="BU27" s="22"/>
-      <c r="BW27" s="22"/>
-      <c r="BX27" s="10"/>
-      <c r="BY27" s="12"/>
-      <c r="BZ27" s="22"/>
+      <c r="BG27" s="22"/>
+      <c r="BH27" s="9"/>
+      <c r="BI27" s="5"/>
+      <c r="BJ27" s="22"/>
+      <c r="BK27" s="9"/>
+      <c r="BL27" s="22"/>
+      <c r="BM27" s="22"/>
+      <c r="BN27" s="22"/>
+      <c r="BO27" s="6"/>
+      <c r="BP27" s="13"/>
+      <c r="BQ27" s="23"/>
+      <c r="BR27" s="23"/>
+      <c r="BS27" s="6"/>
+      <c r="BT27" s="13"/>
+      <c r="BU27" s="23"/>
+      <c r="BV27" s="23"/>
+      <c r="BW27" s="23"/>
+      <c r="BX27" s="6"/>
+      <c r="BY27" s="13"/>
+      <c r="BZ27" s="23"/>
+      <c r="CA27" s="23"/>
+      <c r="CB27" s="12"/>
     </row>
     <row r="28">
-      <c r="B28" s="33"/>
-      <c r="G28" s="34"/>
+      <c r="B28" s="12"/>
+      <c r="G28" s="31"/>
       <c r="H28" s="20" t="inlineStr">
         <is>
           <t>集計整理</t>
@@ -2717,67 +3056,84 @@
       <c r="Q28" s="17"/>
       <c r="R28" s="17"/>
       <c r="S28" s="19"/>
-      <c r="T28" s="40" t="inlineStr">
+      <c r="T28" s="38" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
       <c r="U28" s="19"/>
-      <c r="W28" s="2" t="inlineStr">
+      <c r="V28" s="9"/>
+      <c r="W28" s="26" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="AC28" s="16"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="4"/>
+      <c r="Z28" s="5"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="5"/>
+      <c r="AC28" s="9"/>
       <c r="AD28" s="17"/>
       <c r="AE28" s="21" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="AF28" s="23"/>
+      <c r="AF28" s="24"/>
       <c r="AG28" s="16"/>
       <c r="AH28" s="19"/>
-      <c r="AI28" s="23"/>
+      <c r="AI28" s="24"/>
+      <c r="AJ28" s="24"/>
       <c r="AK28" s="16"/>
       <c r="AL28" s="19"/>
-      <c r="AM28" s="23"/>
+      <c r="AM28" s="24"/>
+      <c r="AN28" s="24"/>
       <c r="AO28" s="16"/>
       <c r="AP28" s="19"/>
-      <c r="AQ28" s="23"/>
+      <c r="AQ28" s="24"/>
       <c r="AR28" s="16"/>
-      <c r="AS28" s="19"/>
-      <c r="AT28" s="23"/>
+      <c r="AS28" s="24"/>
+      <c r="AT28" s="24"/>
+      <c r="AU28" s="24"/>
       <c r="AV28" s="16"/>
       <c r="AW28" s="19"/>
-      <c r="AX28" s="23"/>
+      <c r="AX28" s="24"/>
+      <c r="AY28" s="24"/>
       <c r="AZ28" s="16"/>
       <c r="BA28" s="19"/>
-      <c r="BB28" s="23"/>
+      <c r="BB28" s="24"/>
+      <c r="BC28" s="24"/>
       <c r="BD28" s="16"/>
       <c r="BE28" s="19"/>
-      <c r="BF28" s="23"/>
+      <c r="BF28" s="24"/>
+      <c r="BG28" s="24"/>
       <c r="BH28" s="16"/>
       <c r="BI28" s="19"/>
-      <c r="BJ28" s="24"/>
-      <c r="BK28" s="15"/>
-      <c r="BL28" s="5"/>
-      <c r="BM28" s="24"/>
-      <c r="BO28" s="16"/>
+      <c r="BJ28" s="22"/>
+      <c r="BK28" s="9"/>
+      <c r="BL28" s="22"/>
+      <c r="BM28" s="22"/>
+      <c r="BN28" s="22"/>
+      <c r="BO28" s="9"/>
       <c r="BP28" s="19"/>
-      <c r="BQ28" s="23"/>
+      <c r="BQ28" s="24"/>
+      <c r="BR28" s="24"/>
       <c r="BS28" s="16"/>
       <c r="BT28" s="19"/>
-      <c r="BU28" s="23"/>
-      <c r="BW28" s="23"/>
+      <c r="BU28" s="24"/>
+      <c r="BV28" s="24"/>
+      <c r="BW28" s="24"/>
       <c r="BX28" s="16"/>
       <c r="BY28" s="19"/>
-      <c r="BZ28" s="23"/>
+      <c r="BZ28" s="24"/>
+      <c r="CA28" s="24"/>
+      <c r="CB28" s="12"/>
     </row>
     <row r="29">
-      <c r="B29" s="33"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="27" t="inlineStr">
+      <c r="B29" s="12"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="29" t="inlineStr">
         <is>
           <t>配分結果の整理</t>
         </is>
@@ -2786,79 +3142,94 @@
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="10"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="6"/>
       <c r="O29" s="11"/>
       <c r="P29" s="11"/>
       <c r="Q29" s="11"/>
       <c r="R29" s="11"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="10"/>
-      <c r="U29" s="12"/>
-      <c r="V29" s="15"/>
-      <c r="W29" s="25" t="inlineStr">
+      <c r="S29" s="13"/>
+      <c r="T29" s="6"/>
+      <c r="U29" s="13"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="26" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="X29" s="15"/>
-      <c r="Y29" s="7" t="inlineStr">
+      <c r="X29" s="9"/>
+      <c r="Y29" s="8" t="inlineStr">
         <is>
           <t>8月10日</t>
         </is>
       </c>
       <c r="Z29" s="5"/>
-      <c r="AA29" s="6" t="inlineStr">
+      <c r="AA29" s="7" t="inlineStr">
         <is>
           <t>9月20日</t>
         </is>
       </c>
       <c r="AB29" s="5"/>
-      <c r="AC29" s="10"/>
+      <c r="AC29" s="6"/>
       <c r="AD29" s="11"/>
-      <c r="AE29" s="36" t="inlineStr">
+      <c r="AE29" s="33" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="AF29" s="26" t="inlineStr">
+      <c r="AF29" s="27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG29" s="10"/>
-      <c r="AH29" s="12"/>
-      <c r="AI29" s="22"/>
-      <c r="AK29" s="10"/>
-      <c r="AL29" s="12"/>
-      <c r="AM29" s="22"/>
-      <c r="AO29" s="10"/>
-      <c r="AP29" s="12"/>
-      <c r="AQ29" s="22"/>
-      <c r="AR29" s="10"/>
-      <c r="AS29" s="12"/>
-      <c r="AT29" s="22"/>
-      <c r="AV29" s="10"/>
-      <c r="AW29" s="12"/>
-      <c r="AX29" s="22"/>
-      <c r="AZ29" s="10"/>
-      <c r="BA29" s="12"/>
-      <c r="BB29" s="22"/>
-      <c r="BD29" s="10"/>
-      <c r="BE29" s="12"/>
-      <c r="BF29" s="22"/>
-      <c r="BH29" s="10"/>
-      <c r="BI29" s="12"/>
-      <c r="BO29" s="10"/>
-      <c r="BP29" s="12"/>
-      <c r="BQ29" s="22"/>
-      <c r="BS29" s="10"/>
-      <c r="BT29" s="12"/>
-      <c r="BU29" s="22"/>
-      <c r="BW29" s="22"/>
-      <c r="BX29" s="10"/>
-      <c r="BY29" s="12"/>
-      <c r="BZ29" s="22"/>
+      <c r="AG29" s="6"/>
+      <c r="AH29" s="13"/>
+      <c r="AI29" s="23"/>
+      <c r="AJ29" s="23"/>
+      <c r="AK29" s="6"/>
+      <c r="AL29" s="13"/>
+      <c r="AM29" s="23"/>
+      <c r="AN29" s="23"/>
+      <c r="AO29" s="6"/>
+      <c r="AP29" s="13"/>
+      <c r="AQ29" s="23"/>
+      <c r="AR29" s="6"/>
+      <c r="AS29" s="23"/>
+      <c r="AT29" s="23"/>
+      <c r="AU29" s="23"/>
+      <c r="AV29" s="6"/>
+      <c r="AW29" s="13"/>
+      <c r="AX29" s="23"/>
+      <c r="AY29" s="23"/>
+      <c r="AZ29" s="6"/>
+      <c r="BA29" s="13"/>
+      <c r="BB29" s="23"/>
+      <c r="BC29" s="23"/>
+      <c r="BD29" s="6"/>
+      <c r="BE29" s="13"/>
+      <c r="BF29" s="23"/>
+      <c r="BG29" s="23"/>
+      <c r="BH29" s="6"/>
+      <c r="BI29" s="13"/>
+      <c r="BJ29" s="22"/>
+      <c r="BK29" s="9"/>
+      <c r="BL29" s="22"/>
+      <c r="BM29" s="22"/>
+      <c r="BN29" s="22"/>
+      <c r="BO29" s="6"/>
+      <c r="BP29" s="13"/>
+      <c r="BQ29" s="23"/>
+      <c r="BR29" s="23"/>
+      <c r="BS29" s="6"/>
+      <c r="BT29" s="13"/>
+      <c r="BU29" s="23"/>
+      <c r="BV29" s="23"/>
+      <c r="BW29" s="23"/>
+      <c r="BX29" s="6"/>
+      <c r="BY29" s="13"/>
+      <c r="BZ29" s="23"/>
+      <c r="CA29" s="23"/>
+      <c r="CB29" s="12"/>
     </row>
     <row r="30">
       <c r="B30" s="16"/>
@@ -2883,65 +3254,82 @@
       <c r="Q30" s="17"/>
       <c r="R30" s="17"/>
       <c r="S30" s="19"/>
-      <c r="T30" s="40" t="inlineStr">
+      <c r="T30" s="38" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
       <c r="U30" s="19"/>
-      <c r="W30" s="2" t="inlineStr">
+      <c r="V30" s="9"/>
+      <c r="W30" s="26" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="AC30" s="16"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="5"/>
+      <c r="AA30" s="9"/>
+      <c r="AB30" s="5"/>
+      <c r="AC30" s="9"/>
       <c r="AD30" s="17"/>
       <c r="AE30" s="19"/>
-      <c r="AF30" s="29" t="inlineStr">
+      <c r="AF30" s="39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="AG30" s="16"/>
       <c r="AH30" s="19"/>
-      <c r="AI30" s="23"/>
+      <c r="AI30" s="24"/>
+      <c r="AJ30" s="24"/>
       <c r="AK30" s="16"/>
       <c r="AL30" s="19"/>
-      <c r="AM30" s="23"/>
+      <c r="AM30" s="24"/>
+      <c r="AN30" s="24"/>
       <c r="AO30" s="16"/>
       <c r="AP30" s="19"/>
-      <c r="AQ30" s="23"/>
+      <c r="AQ30" s="24"/>
       <c r="AR30" s="16"/>
-      <c r="AS30" s="19"/>
-      <c r="AT30" s="23"/>
+      <c r="AS30" s="24"/>
+      <c r="AT30" s="24"/>
+      <c r="AU30" s="24"/>
       <c r="AV30" s="16"/>
       <c r="AW30" s="19"/>
-      <c r="AX30" s="23"/>
+      <c r="AX30" s="24"/>
+      <c r="AY30" s="24"/>
       <c r="AZ30" s="16"/>
       <c r="BA30" s="19"/>
-      <c r="BB30" s="23"/>
+      <c r="BB30" s="24"/>
+      <c r="BC30" s="24"/>
       <c r="BD30" s="16"/>
       <c r="BE30" s="19"/>
-      <c r="BF30" s="23"/>
+      <c r="BF30" s="24"/>
+      <c r="BG30" s="24"/>
       <c r="BH30" s="16"/>
       <c r="BI30" s="19"/>
-      <c r="BJ30" s="24"/>
-      <c r="BK30" s="15"/>
-      <c r="BL30" s="5"/>
-      <c r="BM30" s="24"/>
-      <c r="BO30" s="16"/>
+      <c r="BJ30" s="22"/>
+      <c r="BK30" s="9"/>
+      <c r="BL30" s="22"/>
+      <c r="BM30" s="22"/>
+      <c r="BN30" s="22"/>
+      <c r="BO30" s="9"/>
       <c r="BP30" s="19"/>
-      <c r="BQ30" s="23"/>
+      <c r="BQ30" s="24"/>
+      <c r="BR30" s="24"/>
       <c r="BS30" s="16"/>
       <c r="BT30" s="19"/>
-      <c r="BU30" s="23"/>
-      <c r="BW30" s="23"/>
+      <c r="BU30" s="24"/>
+      <c r="BV30" s="24"/>
+      <c r="BW30" s="24"/>
       <c r="BX30" s="16"/>
       <c r="BY30" s="19"/>
-      <c r="BZ30" s="23"/>
+      <c r="BZ30" s="24"/>
+      <c r="CA30" s="24"/>
+      <c r="CB30" s="12"/>
     </row>
     <row r="31">
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>報告書作成</t>
         </is>
@@ -2950,93 +3338,104 @@
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="10"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="6"/>
       <c r="I31" s="11"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="10"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="6"/>
       <c r="O31" s="11"/>
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
       <c r="R31" s="11"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="41" t="inlineStr">
+      <c r="S31" s="13"/>
+      <c r="T31" s="40" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="U31" s="12"/>
-      <c r="V31" s="9" t="inlineStr">
+      <c r="U31" s="13"/>
+      <c r="V31" s="10" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="W31" s="25" t="inlineStr">
+      <c r="W31" s="26" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="X31" s="15"/>
-      <c r="Y31" s="7" t="inlineStr">
+      <c r="X31" s="9"/>
+      <c r="Y31" s="8" t="inlineStr">
         <is>
           <t>10月1日</t>
         </is>
       </c>
       <c r="Z31" s="5"/>
-      <c r="AA31" s="6" t="inlineStr">
+      <c r="AA31" s="7" t="inlineStr">
         <is>
           <t>11月1日</t>
         </is>
       </c>
       <c r="AB31" s="5"/>
-      <c r="AC31" s="10"/>
+      <c r="AC31" s="6"/>
       <c r="AD31" s="11"/>
-      <c r="AE31" s="36" t="inlineStr">
+      <c r="AE31" s="33" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="AF31" s="22"/>
-      <c r="AG31" s="10"/>
-      <c r="AH31" s="12"/>
-      <c r="AI31" s="22"/>
-      <c r="AK31" s="10"/>
-      <c r="AL31" s="12"/>
-      <c r="AM31" s="22"/>
-      <c r="AO31" s="10"/>
-      <c r="AP31" s="12"/>
-      <c r="AQ31" s="22"/>
-      <c r="AR31" s="10"/>
-      <c r="AS31" s="12"/>
-      <c r="AT31" s="22"/>
-      <c r="AV31" s="10"/>
-      <c r="AW31" s="12"/>
-      <c r="AX31" s="22"/>
-      <c r="AZ31" s="10"/>
-      <c r="BA31" s="12"/>
-      <c r="BB31" s="22"/>
-      <c r="BD31" s="10"/>
-      <c r="BE31" s="12"/>
-      <c r="BF31" s="22"/>
-      <c r="BH31" s="10"/>
-      <c r="BI31" s="12"/>
-      <c r="BJ31" s="22"/>
-      <c r="BK31" s="10"/>
-      <c r="BL31" s="12"/>
-      <c r="BM31" s="22"/>
-      <c r="BO31" s="10"/>
-      <c r="BP31" s="12"/>
-      <c r="BQ31" s="24"/>
-      <c r="BS31" s="15"/>
+      <c r="AF31" s="23"/>
+      <c r="AG31" s="6"/>
+      <c r="AH31" s="13"/>
+      <c r="AI31" s="23"/>
+      <c r="AJ31" s="23"/>
+      <c r="AK31" s="6"/>
+      <c r="AL31" s="13"/>
+      <c r="AM31" s="23"/>
+      <c r="AN31" s="23"/>
+      <c r="AO31" s="6"/>
+      <c r="AP31" s="13"/>
+      <c r="AQ31" s="23"/>
+      <c r="AR31" s="6"/>
+      <c r="AS31" s="23"/>
+      <c r="AT31" s="23"/>
+      <c r="AU31" s="23"/>
+      <c r="AV31" s="6"/>
+      <c r="AW31" s="13"/>
+      <c r="AX31" s="23"/>
+      <c r="AY31" s="23"/>
+      <c r="AZ31" s="6"/>
+      <c r="BA31" s="13"/>
+      <c r="BB31" s="23"/>
+      <c r="BC31" s="23"/>
+      <c r="BD31" s="6"/>
+      <c r="BE31" s="13"/>
+      <c r="BF31" s="23"/>
+      <c r="BG31" s="23"/>
+      <c r="BH31" s="6"/>
+      <c r="BI31" s="13"/>
+      <c r="BJ31" s="23"/>
+      <c r="BK31" s="6"/>
+      <c r="BL31" s="23"/>
+      <c r="BM31" s="23"/>
+      <c r="BN31" s="23"/>
+      <c r="BO31" s="6"/>
+      <c r="BP31" s="13"/>
+      <c r="BQ31" s="22"/>
+      <c r="BR31" s="22"/>
+      <c r="BS31" s="9"/>
       <c r="BT31" s="5"/>
-      <c r="BU31" s="22"/>
-      <c r="BW31" s="22"/>
-      <c r="BX31" s="10"/>
-      <c r="BY31" s="12"/>
-      <c r="BZ31" s="22"/>
+      <c r="BU31" s="23"/>
+      <c r="BV31" s="23"/>
+      <c r="BW31" s="23"/>
+      <c r="BX31" s="6"/>
+      <c r="BY31" s="13"/>
+      <c r="BZ31" s="23"/>
+      <c r="CA31" s="23"/>
+      <c r="CB31" s="12"/>
     </row>
     <row r="32">
       <c r="B32" s="16"/>
@@ -3059,56 +3458,76 @@
       <c r="S32" s="19"/>
       <c r="T32" s="16"/>
       <c r="U32" s="19"/>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="V32" s="9"/>
+      <c r="W32" s="26" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="AC32" s="16"/>
+      <c r="X32" s="9"/>
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="5"/>
+      <c r="AA32" s="9"/>
+      <c r="AB32" s="5"/>
+      <c r="AC32" s="9"/>
       <c r="AD32" s="17"/>
       <c r="AE32" s="19"/>
-      <c r="AF32" s="29" t="inlineStr">
+      <c r="AF32" s="39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="AG32" s="16"/>
       <c r="AH32" s="19"/>
-      <c r="AI32" s="23"/>
+      <c r="AI32" s="24"/>
+      <c r="AJ32" s="24"/>
       <c r="AK32" s="16"/>
       <c r="AL32" s="19"/>
-      <c r="AM32" s="23"/>
+      <c r="AM32" s="24"/>
+      <c r="AN32" s="24"/>
       <c r="AO32" s="16"/>
       <c r="AP32" s="19"/>
-      <c r="AQ32" s="23"/>
+      <c r="AQ32" s="24"/>
       <c r="AR32" s="16"/>
-      <c r="AS32" s="19"/>
-      <c r="AT32" s="23"/>
+      <c r="AS32" s="24"/>
+      <c r="AT32" s="24"/>
+      <c r="AU32" s="24"/>
       <c r="AV32" s="16"/>
       <c r="AW32" s="19"/>
-      <c r="AX32" s="23"/>
+      <c r="AX32" s="24"/>
+      <c r="AY32" s="24"/>
       <c r="AZ32" s="16"/>
       <c r="BA32" s="19"/>
-      <c r="BB32" s="23"/>
+      <c r="BB32" s="24"/>
+      <c r="BC32" s="24"/>
       <c r="BD32" s="16"/>
       <c r="BE32" s="19"/>
-      <c r="BF32" s="23"/>
+      <c r="BF32" s="24"/>
+      <c r="BG32" s="24"/>
       <c r="BH32" s="16"/>
       <c r="BI32" s="19"/>
-      <c r="BJ32" s="23"/>
+      <c r="BJ32" s="24"/>
       <c r="BK32" s="16"/>
-      <c r="BL32" s="19"/>
-      <c r="BM32" s="23"/>
+      <c r="BL32" s="24"/>
+      <c r="BM32" s="24"/>
+      <c r="BN32" s="24"/>
       <c r="BO32" s="16"/>
       <c r="BP32" s="19"/>
-      <c r="BU32" s="23"/>
-      <c r="BW32" s="23"/>
+      <c r="BQ32" s="22"/>
+      <c r="BR32" s="22"/>
+      <c r="BS32" s="9"/>
+      <c r="BT32" s="5"/>
+      <c r="BU32" s="22"/>
+      <c r="BV32" s="24"/>
+      <c r="BW32" s="24"/>
       <c r="BX32" s="16"/>
       <c r="BY32" s="19"/>
-      <c r="BZ32" s="23"/>
+      <c r="BZ32" s="24"/>
+      <c r="CA32" s="24"/>
+      <c r="CB32" s="12"/>
     </row>
     <row r="33">
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>照査</t>
         </is>
@@ -3118,97 +3537,189 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="5"/>
-      <c r="H33" s="15"/>
+      <c r="H33" s="9"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="15"/>
+      <c r="N33" s="9"/>
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
       <c r="R33" s="4"/>
       <c r="S33" s="5"/>
-      <c r="T33" s="39" t="inlineStr">
+      <c r="T33" s="37" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
       <c r="U33" s="5"/>
-      <c r="V33" s="9" t="inlineStr">
+      <c r="V33" s="10" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="W33" s="25" t="inlineStr">
+      <c r="W33" s="26" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="X33" s="15"/>
+      <c r="X33" s="9"/>
       <c r="Y33" s="4"/>
       <c r="Z33" s="5"/>
-      <c r="AA33" s="15"/>
+      <c r="AA33" s="9"/>
       <c r="AB33" s="5"/>
-      <c r="AC33" s="15"/>
+      <c r="AC33" s="9"/>
       <c r="AD33" s="4"/>
       <c r="AE33" s="5"/>
-      <c r="AF33" s="32" t="inlineStr">
+      <c r="AF33" s="25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG33" s="15"/>
+      <c r="AG33" s="9"/>
       <c r="AH33" s="5"/>
-      <c r="AI33" s="24"/>
-      <c r="AK33" s="15"/>
+      <c r="AI33" s="22"/>
+      <c r="AJ33" s="22"/>
+      <c r="AK33" s="9"/>
       <c r="AL33" s="5"/>
-      <c r="AM33" s="24"/>
-      <c r="AO33" s="15"/>
+      <c r="AM33" s="22"/>
+      <c r="AN33" s="22"/>
+      <c r="AO33" s="9"/>
       <c r="AP33" s="5"/>
-      <c r="AQ33" s="24"/>
-      <c r="AR33" s="15"/>
-      <c r="AS33" s="5"/>
-      <c r="AT33" s="24"/>
-      <c r="AV33" s="15"/>
+      <c r="AQ33" s="22"/>
+      <c r="AR33" s="9"/>
+      <c r="AS33" s="22"/>
+      <c r="AT33" s="22"/>
+      <c r="AU33" s="22"/>
+      <c r="AV33" s="9"/>
       <c r="AW33" s="5"/>
-      <c r="AX33" s="24"/>
-      <c r="AZ33" s="15"/>
+      <c r="AX33" s="22"/>
+      <c r="AY33" s="22"/>
+      <c r="AZ33" s="9"/>
       <c r="BA33" s="5"/>
-      <c r="BB33" s="24"/>
-      <c r="BD33" s="15"/>
+      <c r="BB33" s="22"/>
+      <c r="BC33" s="22"/>
+      <c r="BD33" s="9"/>
       <c r="BE33" s="5"/>
-      <c r="BF33" s="24"/>
-      <c r="BH33" s="15"/>
+      <c r="BF33" s="22"/>
+      <c r="BG33" s="22"/>
+      <c r="BH33" s="9"/>
       <c r="BI33" s="5"/>
-      <c r="BJ33" s="24"/>
-      <c r="BK33" s="15"/>
-      <c r="BL33" s="5"/>
-      <c r="BM33" s="24"/>
-      <c r="BO33" s="15"/>
+      <c r="BJ33" s="22"/>
+      <c r="BK33" s="9"/>
+      <c r="BL33" s="22"/>
+      <c r="BM33" s="22"/>
+      <c r="BN33" s="22"/>
+      <c r="BO33" s="9"/>
       <c r="BP33" s="5"/>
-      <c r="BQ33" s="24"/>
-      <c r="BS33" s="15"/>
+      <c r="BQ33" s="22"/>
+      <c r="BR33" s="22"/>
+      <c r="BS33" s="9"/>
       <c r="BT33" s="5"/>
-      <c r="BU33" s="24"/>
-      <c r="BW33" s="24"/>
-      <c r="BX33" s="15"/>
+      <c r="BU33" s="22"/>
+      <c r="BV33" s="22"/>
+      <c r="BW33" s="22"/>
+      <c r="BX33" s="9"/>
       <c r="BY33" s="5"/>
-      <c r="BZ33" s="24"/>
+      <c r="BZ33" s="22"/>
+      <c r="CA33" s="22"/>
+      <c r="CB33" s="12"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="6"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
+      <c r="T34" s="6"/>
+      <c r="U34" s="11"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="11"/>
+      <c r="X34" s="6"/>
+      <c r="Y34" s="11"/>
+      <c r="Z34" s="11"/>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="11"/>
+      <c r="AC34" s="6"/>
+      <c r="AD34" s="11"/>
+      <c r="AE34" s="11"/>
+      <c r="AF34" s="6"/>
+      <c r="AG34" s="6"/>
+      <c r="AH34" s="11"/>
+      <c r="AI34" s="6"/>
+      <c r="AJ34" s="6"/>
+      <c r="AK34" s="6"/>
+      <c r="AL34" s="11"/>
+      <c r="AM34" s="6"/>
+      <c r="AN34" s="6"/>
+      <c r="AO34" s="6"/>
+      <c r="AP34" s="11"/>
+      <c r="AQ34" s="6"/>
+      <c r="AR34" s="6"/>
+      <c r="AS34" s="6"/>
+      <c r="AT34" s="11"/>
+      <c r="AU34" s="6"/>
+      <c r="AV34" s="6"/>
+      <c r="AW34" s="11"/>
+      <c r="AX34" s="6"/>
+      <c r="AY34" s="6"/>
+      <c r="AZ34" s="6"/>
+      <c r="BA34" s="11"/>
+      <c r="BB34" s="6"/>
+      <c r="BC34" s="6"/>
+      <c r="BD34" s="6"/>
+      <c r="BE34" s="11"/>
+      <c r="BF34" s="6"/>
+      <c r="BG34" s="6"/>
+      <c r="BH34" s="6"/>
+      <c r="BI34" s="11"/>
+      <c r="BJ34" s="6"/>
+      <c r="BK34" s="6"/>
+      <c r="BL34" s="6"/>
+      <c r="BM34" s="11"/>
+      <c r="BN34" s="6"/>
+      <c r="BO34" s="6"/>
+      <c r="BP34" s="11"/>
+      <c r="BQ34" s="6"/>
+      <c r="BR34" s="6"/>
+      <c r="BS34" s="6"/>
+      <c r="BT34" s="11"/>
+      <c r="BU34" s="6"/>
+      <c r="BV34" s="6"/>
+      <c r="BW34" s="6"/>
+      <c r="BX34" s="6"/>
+      <c r="BY34" s="11"/>
+      <c r="BZ34" s="6"/>
+      <c r="CA34" s="6"/>
+      <c r="CB34" s="12"/>
     </row>
     <row r="35">
-      <c r="B35" s="10"/>
-      <c r="C35" s="42" t="inlineStr">
+      <c r="B35" s="6"/>
+      <c r="C35" s="41" t="inlineStr">
         <is>
           <t>行追加</t>
         </is>
       </c>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="12"/>
-      <c r="K35" s="14" t="inlineStr">
+      <c r="F35" s="6"/>
+      <c r="G35" s="23"/>
+      <c r="K35" s="15" t="inlineStr">
         <is>
           <t>必要に応じて行を追加</t>
         </is>
@@ -3220,10 +3731,10 @@
       <c r="P35" s="11"/>
       <c r="Q35" s="11"/>
       <c r="R35" s="11"/>
-      <c r="S35" s="12"/>
-      <c r="AF35" s="15"/>
+      <c r="S35" s="23"/>
+      <c r="AF35" s="9"/>
       <c r="AG35" s="4"/>
-      <c r="AH35" s="5"/>
+      <c r="AH35" s="22"/>
       <c r="AI35" s="2" t="inlineStr">
         <is>
           <t>計画</t>
@@ -3231,21 +3742,24 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="16"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="19"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="19"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="22"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="4"/>
+      <c r="R36" s="4"/>
+      <c r="S36" s="22"/>
+      <c r="AF36" s="9"/>
+      <c r="AG36" s="4"/>
+      <c r="AH36" s="22"/>
       <c r="AI36" s="2" t="inlineStr">
         <is>
           <t>実績</t>
@@ -3253,12 +3767,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="43" t="inlineStr">
+      <c r="B37" s="42" t="inlineStr">
         <is>
           <t>【3.作業事項及び対応状況等】</t>
         </is>
       </c>
-      <c r="C37" s="15"/>
+      <c r="C37" s="9"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -3275,30 +3789,30 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
       <c r="S37" s="5"/>
-      <c r="T37" s="15"/>
+      <c r="T37" s="9"/>
       <c r="U37" s="5"/>
-      <c r="V37" s="6" t="inlineStr">
+      <c r="V37" s="7" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
       <c r="W37" s="4"/>
       <c r="X37" s="4"/>
-      <c r="Y37" s="7" t="inlineStr">
+      <c r="Y37" s="8" t="inlineStr">
         <is>
           <t>受注者</t>
         </is>
       </c>
       <c r="Z37" s="5"/>
-      <c r="AA37" s="15"/>
+      <c r="AA37" s="9"/>
       <c r="AB37" s="5"/>
-      <c r="AC37" s="15"/>
+      <c r="AC37" s="9"/>
       <c r="AD37" s="4"/>
       <c r="AE37" s="5"/>
-      <c r="AF37" s="15"/>
+      <c r="AF37" s="9"/>
       <c r="AG37" s="4"/>
-      <c r="AH37" s="5"/>
-      <c r="AI37" s="10"/>
+      <c r="AH37" s="22"/>
+      <c r="AI37" s="6"/>
       <c r="AJ37" s="11"/>
       <c r="AK37" s="11"/>
       <c r="AL37" s="11"/>
@@ -3309,10 +3823,11 @@
       <c r="AQ37" s="11"/>
       <c r="AR37" s="11"/>
       <c r="AS37" s="11"/>
-      <c r="AT37" s="12"/>
+      <c r="AT37" s="13"/>
+      <c r="AU37" s="6"/>
     </row>
     <row r="38">
-      <c r="B38" s="29" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>No,</t>
         </is>
@@ -3344,24 +3859,24 @@
         </is>
       </c>
       <c r="U38" s="19"/>
-      <c r="V38" s="9" t="inlineStr">
+      <c r="V38" s="10" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="W38" s="25" t="inlineStr">
+      <c r="W38" s="26" t="inlineStr">
         <is>
           <t>作業担当</t>
         </is>
       </c>
-      <c r="X38" s="9" t="inlineStr">
+      <c r="X38" s="10" t="inlineStr">
         <is>
           <t>受注者</t>
         </is>
       </c>
       <c r="Y38" s="4"/>
       <c r="Z38" s="5"/>
-      <c r="AA38" s="20" t="inlineStr">
+      <c r="AA38" s="7" t="inlineStr">
         <is>
           <t>依頼日</t>
         </is>
@@ -3380,7 +3895,7 @@
           <t>期限</t>
         </is>
       </c>
-      <c r="AH38" s="19"/>
+      <c r="AH38" s="24"/>
       <c r="AI38" s="16"/>
       <c r="AJ38" s="17"/>
       <c r="AK38" s="17"/>
@@ -3397,14 +3912,15 @@
       <c r="AR38" s="17"/>
       <c r="AS38" s="17"/>
       <c r="AT38" s="19"/>
+      <c r="AU38" s="12"/>
     </row>
     <row r="39">
-      <c r="B39" s="32" t="inlineStr">
+      <c r="B39" s="25" t="inlineStr">
         <is>
           <t>1着手時、経歴書、技術者届等</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>着手時、経歴書、技術者届等</t>
         </is>
@@ -3425,38 +3941,42 @@
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
       <c r="S39" s="5"/>
-      <c r="T39" s="6" t="inlineStr">
+      <c r="T39" s="7" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
       <c r="U39" s="5"/>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="V39" s="9"/>
+      <c r="W39" s="5"/>
+      <c r="X39" s="9"/>
+      <c r="Y39" s="8" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="AA39" s="15"/>
-      <c r="AB39" s="25" t="inlineStr">
+      <c r="Z39" s="5"/>
+      <c r="AA39" s="9"/>
+      <c r="AB39" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AC39" s="15"/>
-      <c r="AD39" s="7" t="inlineStr">
+      <c r="AC39" s="9"/>
+      <c r="AD39" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="AE39" s="5"/>
-      <c r="AF39" s="15"/>
-      <c r="AG39" s="7" t="inlineStr">
+      <c r="AF39" s="9"/>
+      <c r="AG39" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH39" s="5"/>
-      <c r="AI39" s="15"/>
+      <c r="AH39" s="22"/>
+      <c r="AI39" s="9"/>
       <c r="AJ39" s="4"/>
       <c r="AK39" s="4"/>
       <c r="AL39" s="4"/>
@@ -3468,55 +3988,91 @@
       <c r="AR39" s="4"/>
       <c r="AS39" s="4"/>
       <c r="AT39" s="5"/>
+      <c r="AU39" s="6"/>
     </row>
     <row r="40">
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="25" t="inlineStr">
         <is>
           <t>2業務計画書作成</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>業務計画書作成</t>
         </is>
       </c>
-      <c r="T40" s="2" t="inlineStr">
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="7" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="V40" s="15"/>
+      <c r="U40" s="5"/>
+      <c r="V40" s="9"/>
       <c r="W40" s="5"/>
-      <c r="X40" s="15"/>
-      <c r="Y40" s="7" t="inlineStr">
+      <c r="X40" s="9"/>
+      <c r="Y40" s="8" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
       <c r="Z40" s="5"/>
-      <c r="AB40" s="2" t="inlineStr">
+      <c r="AA40" s="9"/>
+      <c r="AB40" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AD40" s="2" t="inlineStr">
+      <c r="AC40" s="9"/>
+      <c r="AD40" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AG40" s="2" t="inlineStr">
+      <c r="AE40" s="5"/>
+      <c r="AF40" s="9"/>
+      <c r="AG40" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="AH40" s="22"/>
+      <c r="AI40" s="9"/>
+      <c r="AJ40" s="4"/>
+      <c r="AK40" s="4"/>
+      <c r="AL40" s="4"/>
+      <c r="AM40" s="4"/>
+      <c r="AN40" s="4"/>
+      <c r="AO40" s="4"/>
+      <c r="AP40" s="4"/>
+      <c r="AQ40" s="4"/>
+      <c r="AR40" s="4"/>
+      <c r="AS40" s="4"/>
+      <c r="AT40" s="5"/>
+      <c r="AU40" s="6"/>
     </row>
     <row r="41">
-      <c r="B41" s="32" t="inlineStr">
+      <c r="B41" s="25" t="inlineStr">
         <is>
           <t>3交通量配分用データの作成</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>交通量配分用データの作成</t>
         </is>
@@ -3537,38 +4093,42 @@
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
       <c r="S41" s="5"/>
-      <c r="T41" s="6" t="inlineStr">
+      <c r="T41" s="7" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
       <c r="U41" s="5"/>
-      <c r="Y41" s="2" t="inlineStr">
+      <c r="V41" s="9"/>
+      <c r="W41" s="5"/>
+      <c r="X41" s="9"/>
+      <c r="Y41" s="8" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="AA41" s="6" t="inlineStr">
+      <c r="Z41" s="5"/>
+      <c r="AA41" s="7" t="inlineStr">
         <is>
           <t>5月20日</t>
         </is>
       </c>
       <c r="AB41" s="5"/>
-      <c r="AC41" s="15"/>
-      <c r="AD41" s="7" t="inlineStr">
+      <c r="AC41" s="9"/>
+      <c r="AD41" s="8" t="inlineStr">
         <is>
           <t>5月23日</t>
         </is>
       </c>
       <c r="AE41" s="5"/>
-      <c r="AF41" s="6" t="inlineStr">
+      <c r="AF41" s="7" t="inlineStr">
         <is>
           <t>6月10日</t>
         </is>
       </c>
       <c r="AG41" s="4"/>
-      <c r="AH41" s="5"/>
-      <c r="AI41" s="15"/>
+      <c r="AH41" s="22"/>
+      <c r="AI41" s="9"/>
       <c r="AJ41" s="4"/>
       <c r="AK41" s="4"/>
       <c r="AL41" s="4"/>
@@ -3580,17 +4140,59 @@
       <c r="AR41" s="4"/>
       <c r="AS41" s="4"/>
       <c r="AT41" s="5"/>
+      <c r="AU41" s="6"/>
     </row>
     <row r="42">
-      <c r="V42" s="15"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="5"/>
+      <c r="T42" s="9"/>
+      <c r="U42" s="5"/>
+      <c r="V42" s="9"/>
       <c r="W42" s="5"/>
-      <c r="X42" s="15"/>
+      <c r="X42" s="9"/>
       <c r="Y42" s="4"/>
       <c r="Z42" s="5"/>
+      <c r="AA42" s="9"/>
+      <c r="AB42" s="5"/>
+      <c r="AC42" s="9"/>
+      <c r="AD42" s="4"/>
+      <c r="AE42" s="5"/>
+      <c r="AF42" s="9"/>
+      <c r="AG42" s="4"/>
+      <c r="AH42" s="22"/>
+      <c r="AI42" s="9"/>
+      <c r="AJ42" s="4"/>
+      <c r="AK42" s="4"/>
+      <c r="AL42" s="4"/>
+      <c r="AM42" s="4"/>
+      <c r="AN42" s="4"/>
+      <c r="AO42" s="4"/>
+      <c r="AP42" s="4"/>
+      <c r="AQ42" s="4"/>
+      <c r="AR42" s="4"/>
+      <c r="AS42" s="4"/>
+      <c r="AT42" s="5"/>
+      <c r="AU42" s="6"/>
     </row>
     <row r="43">
-      <c r="B43" s="24"/>
-      <c r="C43" s="15"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="9"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
@@ -3607,17 +4209,22 @@
       <c r="Q43" s="4"/>
       <c r="R43" s="4"/>
       <c r="S43" s="5"/>
-      <c r="T43" s="15"/>
+      <c r="T43" s="9"/>
       <c r="U43" s="5"/>
-      <c r="AA43" s="15"/>
+      <c r="V43" s="9"/>
+      <c r="W43" s="5"/>
+      <c r="X43" s="9"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="5"/>
+      <c r="AA43" s="9"/>
       <c r="AB43" s="5"/>
-      <c r="AC43" s="15"/>
+      <c r="AC43" s="9"/>
       <c r="AD43" s="4"/>
       <c r="AE43" s="5"/>
-      <c r="AF43" s="15"/>
+      <c r="AF43" s="9"/>
       <c r="AG43" s="4"/>
-      <c r="AH43" s="5"/>
-      <c r="AI43" s="15"/>
+      <c r="AH43" s="22"/>
+      <c r="AI43" s="9"/>
       <c r="AJ43" s="4"/>
       <c r="AK43" s="4"/>
       <c r="AL43" s="4"/>
@@ -3629,53 +4236,55 @@
       <c r="AR43" s="4"/>
       <c r="AS43" s="4"/>
       <c r="AT43" s="5"/>
+      <c r="AU43" s="6"/>
     </row>
     <row r="44">
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="17"/>
-      <c r="T44" s="17"/>
-      <c r="U44" s="17"/>
-      <c r="V44" s="15"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="9"/>
+      <c r="U44" s="5"/>
+      <c r="V44" s="9"/>
       <c r="W44" s="5"/>
-      <c r="X44" s="15"/>
+      <c r="X44" s="9"/>
       <c r="Y44" s="4"/>
       <c r="Z44" s="5"/>
-      <c r="AA44" s="17"/>
-      <c r="AB44" s="17"/>
-      <c r="AC44" s="17"/>
-      <c r="AD44" s="17"/>
-      <c r="AE44" s="17"/>
-      <c r="AF44" s="17"/>
-      <c r="AG44" s="17"/>
-      <c r="AH44" s="17"/>
-      <c r="AI44" s="17"/>
-      <c r="AJ44" s="17"/>
-      <c r="AK44" s="17"/>
-      <c r="AL44" s="17"/>
-      <c r="AM44" s="17"/>
-      <c r="AN44" s="17"/>
-      <c r="AO44" s="17"/>
-      <c r="AP44" s="17"/>
-      <c r="AQ44" s="17"/>
-      <c r="AR44" s="17"/>
-      <c r="AS44" s="17"/>
-      <c r="AT44" s="17"/>
+      <c r="AA44" s="9"/>
+      <c r="AB44" s="5"/>
+      <c r="AC44" s="9"/>
+      <c r="AD44" s="4"/>
+      <c r="AE44" s="5"/>
+      <c r="AF44" s="9"/>
+      <c r="AG44" s="4"/>
+      <c r="AH44" s="22"/>
+      <c r="AI44" s="9"/>
+      <c r="AJ44" s="4"/>
+      <c r="AK44" s="4"/>
+      <c r="AL44" s="4"/>
+      <c r="AM44" s="4"/>
+      <c r="AN44" s="4"/>
+      <c r="AO44" s="4"/>
+      <c r="AP44" s="4"/>
+      <c r="AQ44" s="4"/>
+      <c r="AR44" s="4"/>
+      <c r="AS44" s="4"/>
+      <c r="AT44" s="5"/>
+      <c r="AU44" s="6"/>
     </row>
     <row r="45">
       <c r="B45" s="11"/>
@@ -3698,6 +4307,11 @@
       <c r="S45" s="11"/>
       <c r="T45" s="11"/>
       <c r="U45" s="11"/>
+      <c r="V45" s="11"/>
+      <c r="W45" s="11"/>
+      <c r="X45" s="11"/>
+      <c r="Y45" s="11"/>
+      <c r="Z45" s="11"/>
       <c r="AA45" s="11"/>
       <c r="AB45" s="11"/>
       <c r="AC45" s="11"/>
@@ -3718,6 +4332,7 @@
       <c r="AR45" s="11"/>
       <c r="AS45" s="11"/>
       <c r="AT45" s="11"/>
+      <c r="AU45" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.43" right="0.43" top="0.41" bottom="0.41" header="0.5" footer="0.5"/>

--- a/data/out/test2/001317375_Python版_2pt.xlsx
+++ b/data/out/test2/001317375_Python版_2pt.xlsx
@@ -28,29 +28,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="8.300000000000001"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="6.5"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="6"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <color rgb="00FFFFFF"/>
       <sz val="6.5"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <color rgb="00FF0000"/>
       <sz val="6.5"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <color rgb="000000FF"/>
       <sz val="6.5"/>
     </font>
@@ -168,106 +168,106 @@
   <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -635,81 +635,81 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:BU46"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="2.74" defaultRowHeight="18.25" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="2.65" defaultRowHeight="18.25" customHeight="1"/>
   <cols>
-    <col width="2.74" customWidth="1" min="1" max="1"/>
-    <col width="2.74" customWidth="1" min="2" max="2"/>
-    <col width="2.74" customWidth="1" min="3" max="3"/>
-    <col width="2.74" customWidth="1" min="4" max="4"/>
-    <col width="2.74" customWidth="1" min="5" max="5"/>
-    <col width="2.74" customWidth="1" min="6" max="6"/>
-    <col width="2.74" customWidth="1" min="7" max="7"/>
-    <col width="2.74" customWidth="1" min="8" max="8"/>
-    <col width="2.74" customWidth="1" min="9" max="9"/>
-    <col width="2.74" customWidth="1" min="10" max="10"/>
-    <col width="2.74" customWidth="1" min="11" max="11"/>
-    <col width="2.74" customWidth="1" min="12" max="12"/>
-    <col width="2.74" customWidth="1" min="13" max="13"/>
-    <col width="2.74" customWidth="1" min="14" max="14"/>
-    <col width="2.74" customWidth="1" min="15" max="15"/>
-    <col width="2.74" customWidth="1" min="16" max="16"/>
-    <col width="2.74" customWidth="1" min="17" max="17"/>
-    <col width="2.74" customWidth="1" min="18" max="18"/>
-    <col width="2.74" customWidth="1" min="19" max="19"/>
-    <col width="2.74" customWidth="1" min="20" max="20"/>
-    <col width="2.74" customWidth="1" min="21" max="21"/>
-    <col width="2.74" customWidth="1" min="22" max="22"/>
-    <col width="2.74" customWidth="1" min="23" max="23"/>
-    <col width="2.74" customWidth="1" min="24" max="24"/>
-    <col width="2.74" customWidth="1" min="25" max="25"/>
-    <col width="2.74" customWidth="1" min="26" max="26"/>
-    <col width="2.74" customWidth="1" min="27" max="27"/>
-    <col width="2.74" customWidth="1" min="28" max="28"/>
-    <col width="2.74" customWidth="1" min="29" max="29"/>
-    <col width="2.74" customWidth="1" min="30" max="30"/>
-    <col width="2.74" customWidth="1" min="31" max="31"/>
-    <col width="2.74" customWidth="1" min="32" max="32"/>
-    <col width="2.74" customWidth="1" min="33" max="33"/>
-    <col width="2.74" customWidth="1" min="34" max="34"/>
-    <col width="2.74" customWidth="1" min="35" max="35"/>
-    <col width="2.74" customWidth="1" min="36" max="36"/>
-    <col width="2.74" customWidth="1" min="37" max="37"/>
-    <col width="2.74" customWidth="1" min="38" max="38"/>
-    <col width="2.74" customWidth="1" min="39" max="39"/>
-    <col width="2.74" customWidth="1" min="40" max="40"/>
-    <col width="2.74" customWidth="1" min="41" max="41"/>
-    <col width="2.74" customWidth="1" min="42" max="42"/>
-    <col width="2.74" customWidth="1" min="43" max="43"/>
-    <col width="2.74" customWidth="1" min="44" max="44"/>
-    <col width="2.74" customWidth="1" min="45" max="45"/>
-    <col width="2.74" customWidth="1" min="46" max="46"/>
-    <col width="2.74" customWidth="1" min="47" max="47"/>
-    <col width="2.74" customWidth="1" min="48" max="48"/>
-    <col width="2.74" customWidth="1" min="49" max="49"/>
-    <col width="2.74" customWidth="1" min="50" max="50"/>
-    <col width="2.74" customWidth="1" min="51" max="51"/>
-    <col width="2.74" customWidth="1" min="52" max="52"/>
-    <col width="2.74" customWidth="1" min="53" max="53"/>
-    <col width="2.74" customWidth="1" min="54" max="54"/>
-    <col width="2.74" customWidth="1" min="55" max="55"/>
-    <col width="2.74" customWidth="1" min="56" max="56"/>
-    <col width="2.74" customWidth="1" min="57" max="57"/>
-    <col width="2.74" customWidth="1" min="58" max="58"/>
-    <col width="2.74" customWidth="1" min="59" max="59"/>
-    <col width="2.74" customWidth="1" min="60" max="60"/>
-    <col width="2.74" customWidth="1" min="61" max="61"/>
-    <col width="2.74" customWidth="1" min="62" max="62"/>
-    <col width="2.74" customWidth="1" min="63" max="63"/>
-    <col width="2.74" customWidth="1" min="64" max="64"/>
-    <col width="2.74" customWidth="1" min="65" max="65"/>
-    <col width="2.74" customWidth="1" min="66" max="66"/>
-    <col width="2.74" customWidth="1" min="67" max="67"/>
-    <col width="2.74" customWidth="1" min="68" max="68"/>
-    <col width="2.74" customWidth="1" min="69" max="69"/>
-    <col width="2.74" customWidth="1" min="70" max="70"/>
-    <col width="2.74" customWidth="1" min="71" max="71"/>
-    <col width="2.74" customWidth="1" min="72" max="72"/>
-    <col width="2.74" customWidth="1" min="73" max="73"/>
+    <col width="2.65" customWidth="1" min="1" max="1"/>
+    <col width="2.65" customWidth="1" min="2" max="2"/>
+    <col width="2.65" customWidth="1" min="3" max="3"/>
+    <col width="2.65" customWidth="1" min="4" max="4"/>
+    <col width="2.65" customWidth="1" min="5" max="5"/>
+    <col width="2.65" customWidth="1" min="6" max="6"/>
+    <col width="2.65" customWidth="1" min="7" max="7"/>
+    <col width="2.65" customWidth="1" min="8" max="8"/>
+    <col width="2.65" customWidth="1" min="9" max="9"/>
+    <col width="2.65" customWidth="1" min="10" max="10"/>
+    <col width="2.65" customWidth="1" min="11" max="11"/>
+    <col width="2.65" customWidth="1" min="12" max="12"/>
+    <col width="2.65" customWidth="1" min="13" max="13"/>
+    <col width="2.65" customWidth="1" min="14" max="14"/>
+    <col width="2.65" customWidth="1" min="15" max="15"/>
+    <col width="2.65" customWidth="1" min="16" max="16"/>
+    <col width="2.65" customWidth="1" min="17" max="17"/>
+    <col width="2.65" customWidth="1" min="18" max="18"/>
+    <col width="2.65" customWidth="1" min="19" max="19"/>
+    <col width="2.65" customWidth="1" min="20" max="20"/>
+    <col width="2.65" customWidth="1" min="21" max="21"/>
+    <col width="2.65" customWidth="1" min="22" max="22"/>
+    <col width="2.65" customWidth="1" min="23" max="23"/>
+    <col width="2.65" customWidth="1" min="24" max="24"/>
+    <col width="2.65" customWidth="1" min="25" max="25"/>
+    <col width="2.65" customWidth="1" min="26" max="26"/>
+    <col width="2.65" customWidth="1" min="27" max="27"/>
+    <col width="2.65" customWidth="1" min="28" max="28"/>
+    <col width="2.65" customWidth="1" min="29" max="29"/>
+    <col width="2.65" customWidth="1" min="30" max="30"/>
+    <col width="2.65" customWidth="1" min="31" max="31"/>
+    <col width="2.65" customWidth="1" min="32" max="32"/>
+    <col width="2.65" customWidth="1" min="33" max="33"/>
+    <col width="2.65" customWidth="1" min="34" max="34"/>
+    <col width="2.65" customWidth="1" min="35" max="35"/>
+    <col width="2.65" customWidth="1" min="36" max="36"/>
+    <col width="2.65" customWidth="1" min="37" max="37"/>
+    <col width="2.65" customWidth="1" min="38" max="38"/>
+    <col width="2.65" customWidth="1" min="39" max="39"/>
+    <col width="2.65" customWidth="1" min="40" max="40"/>
+    <col width="2.65" customWidth="1" min="41" max="41"/>
+    <col width="2.65" customWidth="1" min="42" max="42"/>
+    <col width="2.65" customWidth="1" min="43" max="43"/>
+    <col width="2.65" customWidth="1" min="44" max="44"/>
+    <col width="2.65" customWidth="1" min="45" max="45"/>
+    <col width="2.65" customWidth="1" min="46" max="46"/>
+    <col width="2.65" customWidth="1" min="47" max="47"/>
+    <col width="2.65" customWidth="1" min="48" max="48"/>
+    <col width="2.65" customWidth="1" min="49" max="49"/>
+    <col width="2.65" customWidth="1" min="50" max="50"/>
+    <col width="2.65" customWidth="1" min="51" max="51"/>
+    <col width="2.65" customWidth="1" min="52" max="52"/>
+    <col width="2.65" customWidth="1" min="53" max="53"/>
+    <col width="2.65" customWidth="1" min="54" max="54"/>
+    <col width="2.65" customWidth="1" min="55" max="55"/>
+    <col width="2.65" customWidth="1" min="56" max="56"/>
+    <col width="2.65" customWidth="1" min="57" max="57"/>
+    <col width="2.65" customWidth="1" min="58" max="58"/>
+    <col width="2.65" customWidth="1" min="59" max="59"/>
+    <col width="2.65" customWidth="1" min="60" max="60"/>
+    <col width="2.65" customWidth="1" min="61" max="61"/>
+    <col width="2.65" customWidth="1" min="62" max="62"/>
+    <col width="2.65" customWidth="1" min="63" max="63"/>
+    <col width="2.65" customWidth="1" min="64" max="64"/>
+    <col width="2.65" customWidth="1" min="65" max="65"/>
+    <col width="2.65" customWidth="1" min="66" max="66"/>
+    <col width="2.65" customWidth="1" min="67" max="67"/>
+    <col width="2.65" customWidth="1" min="68" max="68"/>
+    <col width="2.65" customWidth="1" min="69" max="69"/>
+    <col width="2.65" customWidth="1" min="70" max="70"/>
+    <col width="2.65" customWidth="1" min="71" max="71"/>
+    <col width="2.65" customWidth="1" min="72" max="72"/>
+    <col width="2.65" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="2">
